--- a/academias/Laboratorio Clínico - Estadisticos 20222.xlsx
+++ b/academias/Laboratorio Clínico - Estadisticos 20222.xlsx
@@ -531,22 +531,25 @@
         <v>43</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F2">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>93.02</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>6.98</v>
+      </c>
+      <c r="I2" s="2">
+        <v>8.4</v>
       </c>
       <c r="J2">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1117,22 +1120,25 @@
         <v>41</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F19">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="H19" s="1">
-        <v>100</v>
+        <v>17.07</v>
+      </c>
+      <c r="I19" s="2">
+        <v>7.5</v>
       </c>
       <c r="J19">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1181,22 +1187,25 @@
         <v>35</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F21">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="G21" s="1">
-        <v>0</v>
+        <v>82.86</v>
       </c>
       <c r="H21" s="1">
-        <v>100</v>
+        <v>17.14</v>
+      </c>
+      <c r="I21" s="2">
+        <v>8.1</v>
       </c>
       <c r="J21">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -1213,22 +1222,25 @@
         <v>35</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F22">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="G22" s="1">
-        <v>0</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H22" s="1">
-        <v>100</v>
+        <v>14.29</v>
+      </c>
+      <c r="I22" s="2">
+        <v>7.6</v>
       </c>
       <c r="J22">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2021,22 +2033,25 @@
         <v>43</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F2">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>93.02</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>6.98</v>
+      </c>
+      <c r="I2" s="2">
+        <v>8.4</v>
       </c>
       <c r="J2">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -2607,22 +2622,25 @@
         <v>41</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F19">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="H19" s="1">
-        <v>100</v>
+        <v>17.07</v>
+      </c>
+      <c r="I19" s="2">
+        <v>7.5</v>
       </c>
       <c r="J19">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -2671,22 +2689,25 @@
         <v>35</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F21">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="G21" s="1">
-        <v>0</v>
+        <v>82.86</v>
       </c>
       <c r="H21" s="1">
-        <v>100</v>
+        <v>17.14</v>
+      </c>
+      <c r="I21" s="2">
+        <v>8.1</v>
       </c>
       <c r="J21">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -2703,22 +2724,25 @@
         <v>35</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F22">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="G22" s="1">
-        <v>0</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H22" s="1">
-        <v>100</v>
+        <v>14.29</v>
+      </c>
+      <c r="I22" s="2">
+        <v>7.6</v>
       </c>
       <c r="J22">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Laboratorio Clínico - Estadisticos 20222.xlsx
+++ b/academias/Laboratorio Clínico - Estadisticos 20222.xlsx
@@ -1056,22 +1056,25 @@
         <v>43</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F17">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>74.42</v>
       </c>
       <c r="H17" s="1">
-        <v>100</v>
+        <v>25.58</v>
+      </c>
+      <c r="I17" s="2">
+        <v>6.7</v>
       </c>
       <c r="J17">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1088,22 +1091,25 @@
         <v>26</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F18">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>76.92</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>23.08</v>
+      </c>
+      <c r="I18" s="2">
+        <v>7.5</v>
       </c>
       <c r="J18">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1155,22 +1161,25 @@
         <v>43</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F20">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>69.77</v>
       </c>
       <c r="H20" s="1">
-        <v>100</v>
+        <v>30.23</v>
+      </c>
+      <c r="I20" s="2">
+        <v>6.9</v>
       </c>
       <c r="J20">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -2558,22 +2567,25 @@
         <v>43</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F17">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>74.42</v>
       </c>
       <c r="H17" s="1">
-        <v>100</v>
+        <v>25.58</v>
+      </c>
+      <c r="I17" s="2">
+        <v>6.7</v>
       </c>
       <c r="J17">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -2590,22 +2602,25 @@
         <v>26</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F18">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>76.92</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>23.08</v>
+      </c>
+      <c r="I18" s="2">
+        <v>7.5</v>
       </c>
       <c r="J18">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -2657,22 +2672,25 @@
         <v>43</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F20">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>69.77</v>
       </c>
       <c r="H20" s="1">
-        <v>100</v>
+        <v>30.23</v>
+      </c>
+      <c r="I20" s="2">
+        <v>6.9</v>
       </c>
       <c r="J20">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">

--- a/academias/Laboratorio Clínico - Estadisticos 20222.xlsx
+++ b/academias/Laboratorio Clínico - Estadisticos 20222.xlsx
@@ -843,28 +843,28 @@
         <v>26</v>
       </c>
       <c r="D11">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E11">
         <v>24</v>
       </c>
       <c r="F11">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G11" s="1">
-        <v>68.56999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="H11" s="1">
-        <v>31.43</v>
+        <v>33.33</v>
       </c>
       <c r="I11" s="2">
         <v>7.3</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" s="1">
-        <v>0</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1193,28 +1193,28 @@
         <v>27</v>
       </c>
       <c r="D21">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E21">
         <v>29</v>
       </c>
       <c r="F21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G21" s="1">
-        <v>82.86</v>
+        <v>80.56</v>
       </c>
       <c r="H21" s="1">
-        <v>17.14</v>
+        <v>19.44</v>
       </c>
       <c r="I21" s="2">
         <v>8.1</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" s="1">
-        <v>0</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -1228,28 +1228,28 @@
         <v>28</v>
       </c>
       <c r="D22">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E22">
         <v>30</v>
       </c>
       <c r="F22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G22" s="1">
-        <v>85.70999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="H22" s="1">
-        <v>14.29</v>
+        <v>16.67</v>
       </c>
       <c r="I22" s="2">
         <v>7.6</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" s="1">
-        <v>0</v>
+        <v>2.78</v>
       </c>
     </row>
   </sheetData>
@@ -1603,13 +1603,13 @@
         <v>26</v>
       </c>
       <c r="D11">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E11">
         <v>0</v>
       </c>
       <c r="F11">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
@@ -1618,7 +1618,7 @@
         <v>100</v>
       </c>
       <c r="J11">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K11" s="1">
         <v>100</v>
@@ -1923,13 +1923,13 @@
         <v>27</v>
       </c>
       <c r="D21">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E21">
         <v>0</v>
       </c>
       <c r="F21">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G21" s="1">
         <v>0</v>
@@ -1938,7 +1938,7 @@
         <v>100</v>
       </c>
       <c r="J21">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K21" s="1">
         <v>100</v>
@@ -1955,13 +1955,13 @@
         <v>28</v>
       </c>
       <c r="D22">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E22">
         <v>0</v>
       </c>
       <c r="F22">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G22" s="1">
         <v>0</v>
@@ -1970,7 +1970,7 @@
         <v>100</v>
       </c>
       <c r="J22">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K22" s="1">
         <v>100</v>
@@ -2354,28 +2354,28 @@
         <v>26</v>
       </c>
       <c r="D11">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E11">
         <v>24</v>
       </c>
       <c r="F11">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G11" s="1">
-        <v>68.56999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="H11" s="1">
-        <v>31.43</v>
+        <v>33.33</v>
       </c>
       <c r="I11" s="2">
         <v>6.8</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" s="1">
-        <v>0</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -2704,28 +2704,28 @@
         <v>27</v>
       </c>
       <c r="D21">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E21">
         <v>29</v>
       </c>
       <c r="F21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G21" s="1">
-        <v>82.86</v>
+        <v>80.56</v>
       </c>
       <c r="H21" s="1">
-        <v>17.14</v>
+        <v>19.44</v>
       </c>
       <c r="I21" s="2">
         <v>8.1</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" s="1">
-        <v>0</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -2739,28 +2739,28 @@
         <v>28</v>
       </c>
       <c r="D22">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E22">
         <v>30</v>
       </c>
       <c r="F22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G22" s="1">
-        <v>85.70999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="H22" s="1">
-        <v>14.29</v>
+        <v>16.67</v>
       </c>
       <c r="I22" s="2">
         <v>7.6</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" s="1">
-        <v>0</v>
+        <v>2.78</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Laboratorio Clínico - Estadisticos 20222.xlsx
+++ b/academias/Laboratorio Clínico - Estadisticos 20222.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="34">
   <si>
     <t>Docente</t>
   </si>
@@ -51,18 +51,27 @@
     <t>Por_Blan</t>
   </si>
   <si>
-    <t>Desc Desc Desc</t>
+    <t>Caballero Rosas María Teresa</t>
   </si>
   <si>
     <t>Flores Ovalle Victor</t>
   </si>
   <si>
+    <t>García Sánchez Magda Bexabe</t>
+  </si>
+  <si>
     <t>Martínez Castillo Columba</t>
   </si>
   <si>
+    <t>Mateos Sanchez Jorge</t>
+  </si>
+  <si>
     <t>Rivera Serra Alma Lilian</t>
   </si>
   <si>
+    <t>Ángel Martínez Gerson Hermenegildo</t>
+  </si>
+  <si>
     <t>2ALCM</t>
   </si>
   <si>
@@ -75,6 +84,12 @@
     <t>4BLCM</t>
   </si>
   <si>
+    <t>2ALCV</t>
+  </si>
+  <si>
+    <t>6ALCV</t>
+  </si>
+  <si>
     <t>4ALCV</t>
   </si>
   <si>
@@ -84,28 +99,22 @@
     <t>6BLCM</t>
   </si>
   <si>
-    <t>6ALCV</t>
-  </si>
-  <si>
-    <t>2ALCV</t>
+    <t>TOMA MUESTRAS BIOLÓGICAS</t>
+  </si>
+  <si>
+    <t>REALIZA ANÁLISIS CITOQUÍMICOS A LÍQUIDOS Y SECRECIONES CORPORALES</t>
+  </si>
+  <si>
+    <t>ANALIZA SANGRE CON BASE EN TÉCNICAS DE QUÍMICA CLÍNICA</t>
   </si>
   <si>
     <t>PREPARA SOLUCIONES PARA LAS OPERACIONES BÁSICAS DEL LABORATORIO</t>
   </si>
   <si>
-    <t>TOMA MUESTRAS BIOLÓGICAS</t>
-  </si>
-  <si>
-    <t>REALIZA ANÁLISIS CITOQUÍMICOS A LÍQUIDOS Y SECRECIONES CORPORALES</t>
+    <t>REALIZA ANÁLISIS INMUNOLÓGICOS</t>
   </si>
   <si>
     <t>REALIZA ANÁLISIS HEMATOLÓGICOS DE SERIE ROJA</t>
-  </si>
-  <si>
-    <t>REALIZA ANÁLISIS INMUNOLÓGICOS</t>
-  </si>
-  <si>
-    <t>ANALIZA SANGRE CON BASE EN TÉCNICAS DE QUÍMICA CLÍNICA</t>
   </si>
   <si>
     <t>ANALIZA SANGRE MEDIANTE PRUEBAS HORMONALES, TOXICOLÓGICAS Y DE MARCADORES TUMORALES</t>
@@ -522,28 +531,28 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D2">
         <v>43</v>
       </c>
       <c r="E2">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G2" s="1">
-        <v>93.02</v>
+        <v>86.05</v>
       </c>
       <c r="H2" s="1">
-        <v>6.98</v>
+        <v>13.95</v>
       </c>
       <c r="I2" s="2">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -557,28 +566,28 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D3">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E3">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="F3">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G3" s="1">
-        <v>86.05</v>
+        <v>73.17</v>
       </c>
       <c r="H3" s="1">
-        <v>13.95</v>
+        <v>26.83</v>
       </c>
       <c r="I3" s="2">
-        <v>8</v>
+        <v>6.4</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -592,28 +601,28 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D4">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E4">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F4">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G4" s="1">
-        <v>73.17</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="H4" s="1">
-        <v>26.83</v>
+        <v>4.76</v>
       </c>
       <c r="I4" s="2">
-        <v>6.4</v>
+        <v>8.9</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -627,28 +636,28 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D5">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E5">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5" s="1">
-        <v>95.23999999999999</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="H5" s="1">
-        <v>4.76</v>
+        <v>7.32</v>
       </c>
       <c r="I5" s="2">
-        <v>8.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -659,31 +668,31 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
         <v>27</v>
       </c>
       <c r="D6">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E6">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G6" s="1">
-        <v>100</v>
+        <v>74.42</v>
       </c>
       <c r="H6" s="1">
-        <v>0</v>
+        <v>25.58</v>
       </c>
       <c r="I6" s="2">
-        <v>8.6</v>
+        <v>6.7</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -694,31 +703,31 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D7">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="E7">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="F7">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G7" s="1">
-        <v>92.86</v>
+        <v>76.92</v>
       </c>
       <c r="H7" s="1">
-        <v>7.14</v>
+        <v>23.08</v>
       </c>
       <c r="I7" s="2">
-        <v>8.6</v>
+        <v>7.5</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -729,31 +738,31 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
         <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D8">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E8">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F8">
         <v>3</v>
       </c>
       <c r="G8" s="1">
-        <v>92.68000000000001</v>
+        <v>93.02</v>
       </c>
       <c r="H8" s="1">
-        <v>7.32</v>
+        <v>6.98</v>
       </c>
       <c r="I8" s="2">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -764,31 +773,31 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D9">
         <v>41</v>
       </c>
       <c r="E9">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F9">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G9" s="1">
-        <v>92.68000000000001</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="H9" s="1">
-        <v>7.32</v>
+        <v>17.07</v>
       </c>
       <c r="I9" s="2">
-        <v>8.199999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -799,31 +808,31 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D10">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E10">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G10" s="1">
-        <v>90.23999999999999</v>
+        <v>92.86</v>
       </c>
       <c r="H10" s="1">
-        <v>9.76</v>
+        <v>7.14</v>
       </c>
       <c r="I10" s="2">
-        <v>7.7</v>
+        <v>8.6</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -834,66 +843,66 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D11">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E11">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="F11">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G11" s="1">
-        <v>66.67</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="H11" s="1">
-        <v>33.33</v>
+        <v>7.32</v>
       </c>
       <c r="I11" s="2">
-        <v>7.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C12" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D12">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E12">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G12" s="1">
-        <v>100</v>
+        <v>90.23999999999999</v>
       </c>
       <c r="H12" s="1">
-        <v>0</v>
+        <v>9.76</v>
       </c>
       <c r="I12" s="2">
-        <v>9</v>
+        <v>7.7</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -904,66 +913,66 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D13">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E13">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G13" s="1">
-        <v>100</v>
+        <v>66.67</v>
       </c>
       <c r="H13" s="1">
-        <v>0</v>
+        <v>33.33</v>
       </c>
       <c r="I13" s="2">
-        <v>9</v>
+        <v>7.3</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" s="1">
-        <v>0</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D14">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E14">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" s="1">
-        <v>100</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="H14" s="1">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="I14" s="2">
-        <v>9.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -974,31 +983,31 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" t="s">
         <v>30</v>
       </c>
       <c r="D15">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="E15">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G15" s="1">
-        <v>100</v>
+        <v>69.77</v>
       </c>
       <c r="H15" s="1">
-        <v>0</v>
+        <v>30.23</v>
       </c>
       <c r="I15" s="2">
-        <v>9.5</v>
+        <v>6.9</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -1009,101 +1018,101 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D16">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="E16">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F16">
+        <v>7</v>
+      </c>
+      <c r="G16" s="1">
+        <v>80.56</v>
+      </c>
+      <c r="H16" s="1">
+        <v>19.44</v>
+      </c>
+      <c r="I16" s="2">
+        <v>8.1</v>
+      </c>
+      <c r="J16">
         <v>1</v>
       </c>
-      <c r="G16" s="1">
-        <v>96.15000000000001</v>
-      </c>
-      <c r="H16" s="1">
-        <v>3.85</v>
-      </c>
-      <c r="I16" s="2">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
       <c r="K16" s="1">
-        <v>0</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C17" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D17">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E17">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F17">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G17" s="1">
-        <v>74.42</v>
+        <v>83.33</v>
       </c>
       <c r="H17" s="1">
-        <v>25.58</v>
+        <v>16.67</v>
       </c>
       <c r="I17" s="2">
-        <v>6.7</v>
+        <v>7.6</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" s="1">
-        <v>0</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C18" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D18">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="E18">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="F18">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G18" s="1">
-        <v>76.92</v>
+        <v>100</v>
       </c>
       <c r="H18" s="1">
-        <v>23.08</v>
+        <v>0</v>
       </c>
       <c r="I18" s="2">
-        <v>7.5</v>
+        <v>8.6</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -1114,31 +1123,31 @@
     </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C19" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D19">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="E19">
         <v>34</v>
       </c>
       <c r="F19">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G19" s="1">
-        <v>82.93000000000001</v>
+        <v>100</v>
       </c>
       <c r="H19" s="1">
-        <v>17.07</v>
+        <v>0</v>
       </c>
       <c r="I19" s="2">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -1149,31 +1158,31 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C20" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="D20">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="E20">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F20">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G20" s="1">
-        <v>69.77</v>
+        <v>100</v>
       </c>
       <c r="H20" s="1">
-        <v>30.23</v>
+        <v>0</v>
       </c>
       <c r="I20" s="2">
-        <v>6.9</v>
+        <v>9</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -1184,72 +1193,72 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C21" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D21">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E21">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F21">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G21" s="1">
-        <v>80.56</v>
+        <v>100</v>
       </c>
       <c r="H21" s="1">
-        <v>19.44</v>
+        <v>0</v>
       </c>
       <c r="I21" s="2">
-        <v>8.1</v>
+        <v>9.5</v>
       </c>
       <c r="J21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C22" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D22">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E22">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F22">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G22" s="1">
-        <v>83.33</v>
+        <v>100</v>
       </c>
       <c r="H22" s="1">
-        <v>16.67</v>
+        <v>0</v>
       </c>
       <c r="I22" s="2">
-        <v>7.6</v>
+        <v>9.5</v>
       </c>
       <c r="J22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1309,10 +1318,10 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D2">
         <v>43</v>
@@ -1341,19 +1350,19 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D3">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
@@ -1362,7 +1371,7 @@
         <v>100</v>
       </c>
       <c r="J3">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K3" s="1">
         <v>100</v>
@@ -1373,19 +1382,19 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D4">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
@@ -1394,7 +1403,7 @@
         <v>100</v>
       </c>
       <c r="J4">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K4" s="1">
         <v>100</v>
@@ -1405,19 +1414,19 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D5">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
@@ -1426,7 +1435,7 @@
         <v>100</v>
       </c>
       <c r="J5">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K5" s="1">
         <v>100</v>
@@ -1434,22 +1443,22 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
         <v>27</v>
       </c>
       <c r="D6">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
@@ -1458,7 +1467,7 @@
         <v>100</v>
       </c>
       <c r="J6">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K6" s="1">
         <v>100</v>
@@ -1466,22 +1475,22 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D7">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
@@ -1490,7 +1499,7 @@
         <v>100</v>
       </c>
       <c r="J7">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="K7" s="1">
         <v>100</v>
@@ -1498,22 +1507,22 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
         <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D8">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -1522,7 +1531,7 @@
         <v>100</v>
       </c>
       <c r="J8">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K8" s="1">
         <v>100</v>
@@ -1530,13 +1539,13 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D9">
         <v>41</v>
@@ -1562,22 +1571,22 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D10">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E10">
         <v>0</v>
       </c>
       <c r="F10">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -1586,7 +1595,7 @@
         <v>100</v>
       </c>
       <c r="J10">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K10" s="1">
         <v>100</v>
@@ -1594,22 +1603,22 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D11">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E11">
         <v>0</v>
       </c>
       <c r="F11">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
@@ -1618,7 +1627,7 @@
         <v>100</v>
       </c>
       <c r="J11">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="K11" s="1">
         <v>100</v>
@@ -1626,22 +1635,22 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C12" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D12">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E12">
         <v>0</v>
       </c>
       <c r="F12">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
@@ -1650,7 +1659,7 @@
         <v>100</v>
       </c>
       <c r="J12">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="K12" s="1">
         <v>100</v>
@@ -1658,22 +1667,22 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D13">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E13">
         <v>0</v>
       </c>
       <c r="F13">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
@@ -1682,7 +1691,7 @@
         <v>100</v>
       </c>
       <c r="J13">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K13" s="1">
         <v>100</v>
@@ -1690,22 +1699,22 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D14">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="G14" s="1">
         <v>0</v>
@@ -1714,7 +1723,7 @@
         <v>100</v>
       </c>
       <c r="J14">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="K14" s="1">
         <v>100</v>
@@ -1722,22 +1731,22 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" t="s">
         <v>30</v>
       </c>
       <c r="D15">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="E15">
         <v>0</v>
       </c>
       <c r="F15">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
@@ -1746,7 +1755,7 @@
         <v>100</v>
       </c>
       <c r="J15">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="K15" s="1">
         <v>100</v>
@@ -1754,22 +1763,22 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D16">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="E16">
         <v>0</v>
       </c>
       <c r="F16">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="G16" s="1">
         <v>0</v>
@@ -1778,7 +1787,7 @@
         <v>100</v>
       </c>
       <c r="J16">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="K16" s="1">
         <v>100</v>
@@ -1786,22 +1795,22 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C17" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D17">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E17">
         <v>0</v>
       </c>
       <c r="F17">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="G17" s="1">
         <v>0</v>
@@ -1810,7 +1819,7 @@
         <v>100</v>
       </c>
       <c r="J17">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="K17" s="1">
         <v>100</v>
@@ -1818,22 +1827,22 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C18" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D18">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="E18">
         <v>0</v>
       </c>
       <c r="F18">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="G18" s="1">
         <v>0</v>
@@ -1842,7 +1851,7 @@
         <v>100</v>
       </c>
       <c r="J18">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="K18" s="1">
         <v>100</v>
@@ -1850,22 +1859,22 @@
     </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C19" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D19">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="E19">
         <v>0</v>
       </c>
       <c r="F19">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G19" s="1">
         <v>0</v>
@@ -1874,7 +1883,7 @@
         <v>100</v>
       </c>
       <c r="J19">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="K19" s="1">
         <v>100</v>
@@ -1882,22 +1891,22 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C20" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="D20">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="E20">
         <v>0</v>
       </c>
       <c r="F20">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="G20" s="1">
         <v>0</v>
@@ -1906,7 +1915,7 @@
         <v>100</v>
       </c>
       <c r="J20">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="K20" s="1">
         <v>100</v>
@@ -1914,22 +1923,22 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C21" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D21">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E21">
         <v>0</v>
       </c>
       <c r="F21">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G21" s="1">
         <v>0</v>
@@ -1938,7 +1947,7 @@
         <v>100</v>
       </c>
       <c r="J21">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K21" s="1">
         <v>100</v>
@@ -1946,22 +1955,22 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C22" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D22">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E22">
         <v>0</v>
       </c>
       <c r="F22">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G22" s="1">
         <v>0</v>
@@ -1970,7 +1979,7 @@
         <v>100</v>
       </c>
       <c r="J22">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K22" s="1">
         <v>100</v>
@@ -2033,28 +2042,28 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D2">
         <v>43</v>
       </c>
       <c r="E2">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G2" s="1">
-        <v>93.02</v>
+        <v>86.05</v>
       </c>
       <c r="H2" s="1">
-        <v>6.98</v>
+        <v>13.95</v>
       </c>
       <c r="I2" s="2">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -2068,28 +2077,28 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D3">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E3">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="F3">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G3" s="1">
-        <v>86.05</v>
+        <v>73.17</v>
       </c>
       <c r="H3" s="1">
-        <v>13.95</v>
+        <v>26.83</v>
       </c>
       <c r="I3" s="2">
-        <v>8.199999999999999</v>
+        <v>6.7</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -2103,28 +2112,28 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D4">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E4">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F4">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G4" s="1">
-        <v>73.17</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="H4" s="1">
-        <v>26.83</v>
+        <v>4.76</v>
       </c>
       <c r="I4" s="2">
-        <v>6.7</v>
+        <v>9</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -2138,28 +2147,28 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D5">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E5">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5" s="1">
-        <v>95.23999999999999</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="H5" s="1">
-        <v>4.76</v>
+        <v>7.32</v>
       </c>
       <c r="I5" s="2">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -2170,31 +2179,31 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
         <v>27</v>
       </c>
       <c r="D6">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E6">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G6" s="1">
-        <v>100</v>
+        <v>74.42</v>
       </c>
       <c r="H6" s="1">
-        <v>0</v>
+        <v>25.58</v>
       </c>
       <c r="I6" s="2">
-        <v>8.6</v>
+        <v>6.7</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -2205,31 +2214,31 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D7">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="E7">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="F7">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G7" s="1">
-        <v>92.86</v>
+        <v>76.92</v>
       </c>
       <c r="H7" s="1">
-        <v>7.14</v>
+        <v>23.08</v>
       </c>
       <c r="I7" s="2">
-        <v>8.6</v>
+        <v>7.5</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -2240,31 +2249,31 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
         <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D8">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E8">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F8">
         <v>3</v>
       </c>
       <c r="G8" s="1">
-        <v>92.68000000000001</v>
+        <v>93.02</v>
       </c>
       <c r="H8" s="1">
-        <v>7.32</v>
+        <v>6.98</v>
       </c>
       <c r="I8" s="2">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -2275,31 +2284,31 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D9">
         <v>41</v>
       </c>
       <c r="E9">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F9">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G9" s="1">
-        <v>92.68000000000001</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="H9" s="1">
-        <v>7.32</v>
+        <v>17.07</v>
       </c>
       <c r="I9" s="2">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2310,31 +2319,31 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D10">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E10">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G10" s="1">
-        <v>90.23999999999999</v>
+        <v>92.86</v>
       </c>
       <c r="H10" s="1">
-        <v>9.76</v>
+        <v>7.14</v>
       </c>
       <c r="I10" s="2">
-        <v>7.5</v>
+        <v>8.6</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2345,66 +2354,66 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D11">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E11">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="F11">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G11" s="1">
-        <v>66.67</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="H11" s="1">
-        <v>33.33</v>
+        <v>7.32</v>
       </c>
       <c r="I11" s="2">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C12" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D12">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E12">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G12" s="1">
-        <v>100</v>
+        <v>90.23999999999999</v>
       </c>
       <c r="H12" s="1">
-        <v>0</v>
+        <v>9.76</v>
       </c>
       <c r="I12" s="2">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2415,66 +2424,66 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D13">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E13">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G13" s="1">
-        <v>100</v>
+        <v>66.67</v>
       </c>
       <c r="H13" s="1">
-        <v>0</v>
+        <v>33.33</v>
       </c>
       <c r="I13" s="2">
-        <v>9</v>
+        <v>6.8</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" s="1">
-        <v>0</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D14">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E14">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" s="1">
-        <v>100</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="H14" s="1">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="I14" s="2">
-        <v>9.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2485,31 +2494,31 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" t="s">
         <v>30</v>
       </c>
       <c r="D15">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="E15">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G15" s="1">
-        <v>100</v>
+        <v>69.77</v>
       </c>
       <c r="H15" s="1">
-        <v>0</v>
+        <v>30.23</v>
       </c>
       <c r="I15" s="2">
-        <v>9.5</v>
+        <v>6.9</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2520,101 +2529,101 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D16">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="E16">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F16">
+        <v>7</v>
+      </c>
+      <c r="G16" s="1">
+        <v>80.56</v>
+      </c>
+      <c r="H16" s="1">
+        <v>19.44</v>
+      </c>
+      <c r="I16" s="2">
+        <v>8.1</v>
+      </c>
+      <c r="J16">
         <v>1</v>
       </c>
-      <c r="G16" s="1">
-        <v>96.15000000000001</v>
-      </c>
-      <c r="H16" s="1">
-        <v>3.85</v>
-      </c>
-      <c r="I16" s="2">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
       <c r="K16" s="1">
-        <v>0</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C17" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D17">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E17">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F17">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G17" s="1">
-        <v>74.42</v>
+        <v>83.33</v>
       </c>
       <c r="H17" s="1">
-        <v>25.58</v>
+        <v>16.67</v>
       </c>
       <c r="I17" s="2">
-        <v>6.7</v>
+        <v>7.6</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" s="1">
-        <v>0</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C18" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D18">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="E18">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="F18">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G18" s="1">
-        <v>76.92</v>
+        <v>100</v>
       </c>
       <c r="H18" s="1">
-        <v>23.08</v>
+        <v>0</v>
       </c>
       <c r="I18" s="2">
-        <v>7.5</v>
+        <v>8.6</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -2625,31 +2634,31 @@
     </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C19" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D19">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="E19">
         <v>34</v>
       </c>
       <c r="F19">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G19" s="1">
-        <v>82.93000000000001</v>
+        <v>100</v>
       </c>
       <c r="H19" s="1">
-        <v>17.07</v>
+        <v>0</v>
       </c>
       <c r="I19" s="2">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -2660,31 +2669,31 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C20" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="D20">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="E20">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F20">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G20" s="1">
-        <v>69.77</v>
+        <v>100</v>
       </c>
       <c r="H20" s="1">
-        <v>30.23</v>
+        <v>0</v>
       </c>
       <c r="I20" s="2">
-        <v>6.9</v>
+        <v>9</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -2695,72 +2704,72 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C21" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D21">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E21">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F21">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G21" s="1">
-        <v>80.56</v>
+        <v>100</v>
       </c>
       <c r="H21" s="1">
-        <v>19.44</v>
+        <v>0</v>
       </c>
       <c r="I21" s="2">
-        <v>8.1</v>
+        <v>9.5</v>
       </c>
       <c r="J21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C22" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D22">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E22">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F22">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G22" s="1">
-        <v>83.33</v>
+        <v>100</v>
       </c>
       <c r="H22" s="1">
-        <v>16.67</v>
+        <v>0</v>
       </c>
       <c r="I22" s="2">
-        <v>7.6</v>
+        <v>9.5</v>
       </c>
       <c r="J22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Laboratorio Clínico - Estadisticos 20222.xlsx
+++ b/academias/Laboratorio Clínico - Estadisticos 20222.xlsx
@@ -8,25 +8,24 @@
   </bookViews>
   <sheets>
     <sheet name="1er Parcial" sheetId="1" r:id="rId1"/>
-    <sheet name="2o Parcial" sheetId="2" r:id="rId2"/>
-    <sheet name="Final" sheetId="3" r:id="rId3"/>
+    <sheet name="Final" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="35">
   <si>
     <t>Docente</t>
   </si>
   <si>
+    <t>Mat</t>
+  </si>
+  <si>
     <t>Grupo</t>
   </si>
   <si>
-    <t>Mat</t>
-  </si>
-  <si>
     <t>Totales</t>
   </si>
   <si>
@@ -36,10 +35,10 @@
     <t>Reprobados</t>
   </si>
   <si>
-    <t>Por_Apro</t>
-  </si>
-  <si>
-    <t>Por_Repro</t>
+    <t>por_aprobados</t>
+  </si>
+  <si>
+    <t>por_reprobados</t>
   </si>
   <si>
     <t>Promedio</t>
@@ -48,7 +47,7 @@
     <t>Blancos</t>
   </si>
   <si>
-    <t>Por_Blan</t>
+    <t>por_blancos</t>
   </si>
   <si>
     <t>Caballero Rosas María Teresa</t>
@@ -69,9 +68,33 @@
     <t>Rivera Serra Alma Lilian</t>
   </si>
   <si>
+    <t>Total</t>
+  </si>
+  <si>
     <t>Ángel Martínez Gerson Hermenegildo</t>
   </si>
   <si>
+    <t>TOMA MUESTRAS BIOLÓGICAS</t>
+  </si>
+  <si>
+    <t>REALIZA ANÁLISIS CITOQUÍMICOS A LÍQUIDOS Y SECRECIONES CORPORALES</t>
+  </si>
+  <si>
+    <t>ANALIZA SANGRE CON BASE EN TÉCNICAS DE QUÍMICA CLÍNICA</t>
+  </si>
+  <si>
+    <t>PREPARA SOLUCIONES PARA LAS OPERACIONES BÁSICAS DEL LABORATORIO</t>
+  </si>
+  <si>
+    <t>REALIZA ANÁLISIS INMUNOLÓGICOS</t>
+  </si>
+  <si>
+    <t>REALIZA ANÁLISIS HEMATOLÓGICOS DE SERIE ROJA</t>
+  </si>
+  <si>
+    <t>ANALIZA SANGRE MEDIANTE PRUEBAS HORMONALES, TOXICOLÓGICAS Y DE MARCADORES TUMORALES</t>
+  </si>
+  <si>
     <t>2ALCM</t>
   </si>
   <si>
@@ -97,27 +120,6 @@
   </si>
   <si>
     <t>6BLCM</t>
-  </si>
-  <si>
-    <t>TOMA MUESTRAS BIOLÓGICAS</t>
-  </si>
-  <si>
-    <t>REALIZA ANÁLISIS CITOQUÍMICOS A LÍQUIDOS Y SECRECIONES CORPORALES</t>
-  </si>
-  <si>
-    <t>ANALIZA SANGRE CON BASE EN TÉCNICAS DE QUÍMICA CLÍNICA</t>
-  </si>
-  <si>
-    <t>PREPARA SOLUCIONES PARA LAS OPERACIONES BÁSICAS DEL LABORATORIO</t>
-  </si>
-  <si>
-    <t>REALIZA ANÁLISIS INMUNOLÓGICOS</t>
-  </si>
-  <si>
-    <t>REALIZA ANÁLISIS HEMATOLÓGICOS DE SERIE ROJA</t>
-  </si>
-  <si>
-    <t>ANALIZA SANGRE MEDIANTE PRUEBAS HORMONALES, TOXICOLÓGICAS Y DE MARCADORES TUMORALES</t>
   </si>
 </sst>
 </file>
@@ -481,11 +483,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="30.7109375" customWidth="1"/>
     <col min="7" max="8" width="9.140625" style="1"/>
     <col min="9" max="9" width="9.140625" style="2"/>
     <col min="11" max="11" width="9.140625" style="1"/>
@@ -531,10 +533,10 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D2">
         <v>43</v>
@@ -546,10 +548,10 @@
         <v>6</v>
       </c>
       <c r="G2" s="1">
-        <v>86.05</v>
+        <v>86</v>
       </c>
       <c r="H2" s="1">
-        <v>13.95</v>
+        <v>14</v>
       </c>
       <c r="I2" s="2">
         <v>8</v>
@@ -572,19 +574,19 @@
         <v>27</v>
       </c>
       <c r="D3">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E3">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F3">
         <v>11</v>
       </c>
       <c r="G3" s="1">
-        <v>73.17</v>
+        <v>73.8</v>
       </c>
       <c r="H3" s="1">
-        <v>26.83</v>
+        <v>26.2</v>
       </c>
       <c r="I3" s="2">
         <v>6.4</v>
@@ -616,10 +618,10 @@
         <v>2</v>
       </c>
       <c r="G4" s="1">
-        <v>95.23999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="H4" s="1">
-        <v>4.76</v>
+        <v>4.8</v>
       </c>
       <c r="I4" s="2">
         <v>8.9</v>
@@ -636,10 +638,10 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D5">
         <v>41</v>
@@ -651,10 +653,10 @@
         <v>3</v>
       </c>
       <c r="G5" s="1">
-        <v>92.68000000000001</v>
+        <v>92.7</v>
       </c>
       <c r="H5" s="1">
-        <v>7.32</v>
+        <v>7.3</v>
       </c>
       <c r="I5" s="2">
         <v>8.699999999999999</v>
@@ -668,31 +670,25 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6">
+        <v>168</v>
+      </c>
+      <c r="E6">
+        <v>146</v>
+      </c>
+      <c r="F6">
         <v>22</v>
       </c>
-      <c r="C6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6">
-        <v>43</v>
-      </c>
-      <c r="E6">
-        <v>32</v>
-      </c>
-      <c r="F6">
-        <v>11</v>
-      </c>
       <c r="G6" s="1">
-        <v>74.42</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="H6" s="1">
-        <v>25.58</v>
+        <v>13.1</v>
       </c>
       <c r="I6" s="2">
-        <v>6.7</v>
+        <v>8</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -706,28 +702,28 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D7">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="E7">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F7">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G7" s="1">
-        <v>76.92</v>
+        <v>73.8</v>
       </c>
       <c r="H7" s="1">
-        <v>23.08</v>
+        <v>26.2</v>
       </c>
       <c r="I7" s="2">
-        <v>7.5</v>
+        <v>6.7</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -738,31 +734,31 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D8">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="E8">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F8">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G8" s="1">
-        <v>93.02</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="H8" s="1">
-        <v>6.98</v>
+        <v>23.1</v>
       </c>
       <c r="I8" s="2">
-        <v>8.4</v>
+        <v>7.5</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -773,31 +769,25 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="D9">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="E9">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="F9">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G9" s="1">
-        <v>82.93000000000001</v>
+        <v>75</v>
       </c>
       <c r="H9" s="1">
-        <v>17.07</v>
+        <v>25</v>
       </c>
       <c r="I9" s="2">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -808,31 +798,31 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D10">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E10">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F10">
         <v>3</v>
       </c>
       <c r="G10" s="1">
-        <v>92.86</v>
+        <v>93</v>
       </c>
       <c r="H10" s="1">
-        <v>7.14</v>
+        <v>7</v>
       </c>
       <c r="I10" s="2">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -843,31 +833,25 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="D11">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E11">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F11">
         <v>3</v>
       </c>
       <c r="G11" s="1">
-        <v>92.68000000000001</v>
+        <v>93</v>
       </c>
       <c r="H11" s="1">
-        <v>7.32</v>
+        <v>7</v>
       </c>
       <c r="I11" s="2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -878,31 +862,31 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C12" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D12">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E12">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F12">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G12" s="1">
-        <v>90.23999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="H12" s="1">
-        <v>9.76</v>
+        <v>16.7</v>
       </c>
       <c r="I12" s="2">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -913,37 +897,31 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D13">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E13">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="F13">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G13" s="1">
-        <v>66.67</v>
+        <v>83.3</v>
       </c>
       <c r="H13" s="1">
-        <v>33.33</v>
+        <v>16.7</v>
       </c>
       <c r="I13" s="2">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -954,25 +932,25 @@
         <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D14">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="E14">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="F14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G14" s="1">
-        <v>96.15000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H14" s="1">
-        <v>3.85</v>
+        <v>7.1</v>
       </c>
       <c r="I14" s="2">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -983,31 +961,31 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D15">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E15">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="F15">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="G15" s="1">
-        <v>69.77</v>
+        <v>92.7</v>
       </c>
       <c r="H15" s="1">
-        <v>30.23</v>
+        <v>7.3</v>
       </c>
       <c r="I15" s="2">
-        <v>6.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -1018,66 +996,66 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C16" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D16">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E16">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F16">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G16" s="1">
-        <v>80.56</v>
+        <v>90.2</v>
       </c>
       <c r="H16" s="1">
-        <v>19.44</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I16" s="2">
-        <v>8.1</v>
+        <v>7.7</v>
       </c>
       <c r="J16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C17" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D17">
         <v>36</v>
       </c>
       <c r="E17">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F17">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G17" s="1">
-        <v>83.33</v>
+        <v>66.7</v>
       </c>
       <c r="H17" s="1">
-        <v>16.67</v>
+        <v>33.3</v>
       </c>
       <c r="I17" s="2">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -1088,31 +1066,31 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D18">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="E18">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" s="1">
-        <v>100</v>
+        <v>96.2</v>
       </c>
       <c r="H18" s="1">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="I18" s="2">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -1123,66 +1101,60 @@
     </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>17</v>
-      </c>
-      <c r="B19" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="D19">
-        <v>34</v>
+        <v>186</v>
       </c>
       <c r="E19">
-        <v>34</v>
+        <v>163</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G19" s="1">
-        <v>100</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="H19" s="1">
-        <v>0</v>
+        <v>12.4</v>
       </c>
       <c r="I19" s="2">
-        <v>9</v>
+        <v>8.1</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" s="1">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B20" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C20" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D20">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E20">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G20" s="1">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="H20" s="1">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="I20" s="2">
-        <v>9</v>
+        <v>6.9</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -1193,71 +1165,333 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21">
+        <v>36</v>
+      </c>
+      <c r="E21">
         <v>29</v>
       </c>
-      <c r="D21">
-        <v>32</v>
-      </c>
-      <c r="E21">
-        <v>32</v>
-      </c>
       <c r="F21">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G21" s="1">
-        <v>100</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="H21" s="1">
-        <v>0</v>
+        <v>19.4</v>
       </c>
       <c r="I21" s="2">
-        <v>9.5</v>
+        <v>8.1</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" s="1">
-        <v>0</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22" t="s">
+        <v>23</v>
+      </c>
+      <c r="C22" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22">
+        <v>36</v>
+      </c>
+      <c r="E22">
+        <v>30</v>
+      </c>
+      <c r="F22">
+        <v>6</v>
+      </c>
+      <c r="G22" s="1">
+        <v>83.3</v>
+      </c>
+      <c r="H22" s="1">
+        <v>16.7</v>
+      </c>
+      <c r="I22" s="2">
+        <v>7.6</v>
+      </c>
+      <c r="J22">
+        <v>1</v>
+      </c>
+      <c r="K22" s="1">
+        <v>2.78</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23">
+        <v>114</v>
+      </c>
+      <c r="E23">
+        <v>88</v>
+      </c>
+      <c r="F23">
+        <v>26</v>
+      </c>
+      <c r="G23" s="1">
+        <v>77.2</v>
+      </c>
+      <c r="H23" s="1">
+        <v>22.8</v>
+      </c>
+      <c r="I23" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="J23">
+        <v>2</v>
+      </c>
+      <c r="K23" s="1">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" t="s">
         <v>17</v>
       </c>
-      <c r="B22" t="s">
-        <v>26</v>
-      </c>
-      <c r="C22" t="s">
+      <c r="D24">
+        <v>795</v>
+      </c>
+      <c r="E24">
+        <v>697</v>
+      </c>
+      <c r="F24">
+        <v>98</v>
+      </c>
+      <c r="G24" s="1">
+        <v>87.7</v>
+      </c>
+      <c r="H24" s="1">
+        <v>12.3</v>
+      </c>
+      <c r="I24" s="2">
+        <v>8.1</v>
+      </c>
+      <c r="J24">
+        <v>3</v>
+      </c>
+      <c r="K24" s="1">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" t="s">
+        <v>18</v>
+      </c>
+      <c r="B25" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" t="s">
+        <v>28</v>
+      </c>
+      <c r="D25">
+        <v>42</v>
+      </c>
+      <c r="E25">
+        <v>42</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25" s="1">
+        <v>100</v>
+      </c>
+      <c r="H25" s="1">
+        <v>0</v>
+      </c>
+      <c r="I25" s="2">
+        <v>8.6</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" t="s">
+        <v>18</v>
+      </c>
+      <c r="B26" t="s">
+        <v>21</v>
+      </c>
+      <c r="C26" t="s">
         <v>33</v>
       </c>
-      <c r="D22">
+      <c r="D26">
+        <v>34</v>
+      </c>
+      <c r="E26">
+        <v>34</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26" s="1">
+        <v>100</v>
+      </c>
+      <c r="H26" s="1">
+        <v>0</v>
+      </c>
+      <c r="I26" s="2">
+        <v>9</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" t="s">
+        <v>18</v>
+      </c>
+      <c r="B27" t="s">
+        <v>25</v>
+      </c>
+      <c r="C27" t="s">
+        <v>33</v>
+      </c>
+      <c r="D27">
+        <v>34</v>
+      </c>
+      <c r="E27">
+        <v>34</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27" s="1">
+        <v>100</v>
+      </c>
+      <c r="H27" s="1">
+        <v>0</v>
+      </c>
+      <c r="I27" s="2">
+        <v>9</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" t="s">
+        <v>18</v>
+      </c>
+      <c r="B28" t="s">
+        <v>21</v>
+      </c>
+      <c r="C28" t="s">
+        <v>34</v>
+      </c>
+      <c r="D28">
         <v>32</v>
       </c>
-      <c r="E22">
+      <c r="E28">
         <v>32</v>
       </c>
-      <c r="F22">
-        <v>0</v>
-      </c>
-      <c r="G22" s="1">
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28" s="1">
         <v>100</v>
       </c>
-      <c r="H22" s="1">
-        <v>0</v>
-      </c>
-      <c r="I22" s="2">
+      <c r="H28" s="1">
+        <v>0</v>
+      </c>
+      <c r="I28" s="2">
         <v>9.5</v>
       </c>
-      <c r="J22">
-        <v>0</v>
-      </c>
-      <c r="K22" s="1">
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" t="s">
+        <v>18</v>
+      </c>
+      <c r="B29" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29" t="s">
+        <v>34</v>
+      </c>
+      <c r="D29">
+        <v>32</v>
+      </c>
+      <c r="E29">
+        <v>32</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29" s="1">
+        <v>100</v>
+      </c>
+      <c r="H29" s="1">
+        <v>0</v>
+      </c>
+      <c r="I29" s="2">
+        <v>9.5</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" t="s">
+        <v>18</v>
+      </c>
+      <c r="D30">
+        <v>174</v>
+      </c>
+      <c r="E30">
+        <v>174</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30" s="1">
+        <v>100</v>
+      </c>
+      <c r="H30" s="1">
+        <v>0</v>
+      </c>
+      <c r="I30" s="2">
+        <v>9.1</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1268,11 +1502,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="30.7109375" customWidth="1"/>
     <col min="7" max="8" width="9.140625" style="1"/>
     <col min="9" max="9" width="9.140625" style="2"/>
     <col min="11" max="11" width="9.140625" style="1"/>
@@ -1318,31 +1552,34 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D2">
         <v>43</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F2">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>14</v>
+      </c>
+      <c r="I2" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J2">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1356,25 +1593,28 @@
         <v>27</v>
       </c>
       <c r="D3">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F3">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>73.8</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>26.2</v>
+      </c>
+      <c r="I3" s="2">
+        <v>6.7</v>
       </c>
       <c r="J3">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1391,22 +1631,25 @@
         <v>42</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F4">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>95.2</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>4.8</v>
+      </c>
+      <c r="I4" s="2">
+        <v>9</v>
       </c>
       <c r="J4">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1414,63 +1657,63 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D5">
         <v>41</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F5">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>92.7</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>7.3</v>
+      </c>
+      <c r="I5" s="2">
+        <v>8.800000000000001</v>
       </c>
       <c r="J5">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6">
+        <v>168</v>
+      </c>
+      <c r="E6">
+        <v>146</v>
+      </c>
+      <c r="F6">
         <v>22</v>
       </c>
-      <c r="C6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6">
-        <v>43</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>43</v>
-      </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>13.1</v>
+      </c>
+      <c r="I6" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J6">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1478,223 +1721,226 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D7">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F7">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>73.8</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>26.2</v>
+      </c>
+      <c r="I7" s="2">
+        <v>6.7</v>
       </c>
       <c r="J7">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D8">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F8">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>23.1</v>
+      </c>
+      <c r="I8" s="2">
+        <v>7.5</v>
       </c>
       <c r="J8">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="D9">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="F9">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>25</v>
+      </c>
+      <c r="I9" s="2">
+        <v>7.1</v>
       </c>
       <c r="J9">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D10">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F10">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>7</v>
+      </c>
+      <c r="I10" s="2">
+        <v>8.4</v>
       </c>
       <c r="J10">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="D11">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F11">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>7</v>
+      </c>
+      <c r="I11" s="2">
+        <v>8.4</v>
       </c>
       <c r="J11">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C12" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D12">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F12">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>16.7</v>
+      </c>
+      <c r="I12" s="2">
+        <v>7.5</v>
       </c>
       <c r="J12">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D13">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F13">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>16.7</v>
+      </c>
+      <c r="I13" s="2">
+        <v>7.5</v>
       </c>
       <c r="J13">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1705,1070 +1951,566 @@
         <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D14">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="F14">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>7.1</v>
+      </c>
+      <c r="I14" s="2">
+        <v>8.6</v>
       </c>
       <c r="J14">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D15">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F15">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>92.7</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>7.3</v>
+      </c>
+      <c r="I15" s="2">
+        <v>8</v>
       </c>
       <c r="J15">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C16" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D16">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F16">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>90.2</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>9.800000000000001</v>
+      </c>
+      <c r="I16" s="2">
+        <v>7.5</v>
       </c>
       <c r="J16">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C17" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D17">
         <v>36</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F17">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="H17" s="1">
-        <v>100</v>
+        <v>33.3</v>
+      </c>
+      <c r="I17" s="2">
+        <v>6.8</v>
       </c>
       <c r="J17">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D18">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F18">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>96.2</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>3.8</v>
+      </c>
+      <c r="I18" s="2">
+        <v>8.800000000000001</v>
       </c>
       <c r="J18">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>17</v>
-      </c>
-      <c r="B19" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="D19">
-        <v>34</v>
+        <v>186</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>163</v>
       </c>
       <c r="F19">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="H19" s="1">
-        <v>100</v>
+        <v>12.4</v>
+      </c>
+      <c r="I19" s="2">
+        <v>7.9</v>
       </c>
       <c r="J19">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="K19" s="1">
-        <v>100</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B20" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C20" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D20">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F20">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="H20" s="1">
-        <v>100</v>
+        <v>31</v>
+      </c>
+      <c r="I20" s="2">
+        <v>6.9</v>
       </c>
       <c r="J20">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21">
+        <v>36</v>
+      </c>
+      <c r="E21">
         <v>29</v>
       </c>
-      <c r="D21">
-        <v>32</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
       <c r="F21">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="G21" s="1">
-        <v>0</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="H21" s="1">
-        <v>100</v>
+        <v>19.4</v>
+      </c>
+      <c r="I21" s="2">
+        <v>8.1</v>
       </c>
       <c r="J21">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="K21" s="1">
-        <v>100</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22" t="s">
+        <v>23</v>
+      </c>
+      <c r="C22" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22">
+        <v>36</v>
+      </c>
+      <c r="E22">
+        <v>30</v>
+      </c>
+      <c r="F22">
+        <v>6</v>
+      </c>
+      <c r="G22" s="1">
+        <v>83.3</v>
+      </c>
+      <c r="H22" s="1">
+        <v>16.7</v>
+      </c>
+      <c r="I22" s="2">
+        <v>7.6</v>
+      </c>
+      <c r="J22">
+        <v>1</v>
+      </c>
+      <c r="K22" s="1">
+        <v>2.78</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23">
+        <v>114</v>
+      </c>
+      <c r="E23">
+        <v>88</v>
+      </c>
+      <c r="F23">
+        <v>26</v>
+      </c>
+      <c r="G23" s="1">
+        <v>77.2</v>
+      </c>
+      <c r="H23" s="1">
+        <v>22.8</v>
+      </c>
+      <c r="I23" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="J23">
+        <v>2</v>
+      </c>
+      <c r="K23" s="1">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" t="s">
         <v>17</v>
       </c>
-      <c r="B22" t="s">
-        <v>26</v>
-      </c>
-      <c r="C22" t="s">
+      <c r="D24">
+        <v>795</v>
+      </c>
+      <c r="E24">
+        <v>697</v>
+      </c>
+      <c r="F24">
+        <v>98</v>
+      </c>
+      <c r="G24" s="1">
+        <v>87.7</v>
+      </c>
+      <c r="H24" s="1">
+        <v>12.3</v>
+      </c>
+      <c r="I24" s="2">
+        <v>8.1</v>
+      </c>
+      <c r="J24">
+        <v>3</v>
+      </c>
+      <c r="K24" s="1">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" t="s">
+        <v>18</v>
+      </c>
+      <c r="B25" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" t="s">
+        <v>28</v>
+      </c>
+      <c r="D25">
+        <v>42</v>
+      </c>
+      <c r="E25">
+        <v>42</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25" s="1">
+        <v>100</v>
+      </c>
+      <c r="H25" s="1">
+        <v>0</v>
+      </c>
+      <c r="I25" s="2">
+        <v>8.6</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" t="s">
+        <v>18</v>
+      </c>
+      <c r="B26" t="s">
+        <v>21</v>
+      </c>
+      <c r="C26" t="s">
         <v>33</v>
       </c>
-      <c r="D22">
+      <c r="D26">
+        <v>34</v>
+      </c>
+      <c r="E26">
+        <v>34</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26" s="1">
+        <v>100</v>
+      </c>
+      <c r="H26" s="1">
+        <v>0</v>
+      </c>
+      <c r="I26" s="2">
+        <v>9</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" t="s">
+        <v>18</v>
+      </c>
+      <c r="B27" t="s">
+        <v>25</v>
+      </c>
+      <c r="C27" t="s">
+        <v>33</v>
+      </c>
+      <c r="D27">
+        <v>34</v>
+      </c>
+      <c r="E27">
+        <v>34</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27" s="1">
+        <v>100</v>
+      </c>
+      <c r="H27" s="1">
+        <v>0</v>
+      </c>
+      <c r="I27" s="2">
+        <v>9</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" t="s">
+        <v>18</v>
+      </c>
+      <c r="B28" t="s">
+        <v>21</v>
+      </c>
+      <c r="C28" t="s">
+        <v>34</v>
+      </c>
+      <c r="D28">
         <v>32</v>
       </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-      <c r="F22">
+      <c r="E28">
         <v>32</v>
       </c>
-      <c r="G22" s="1">
-        <v>0</v>
-      </c>
-      <c r="H22" s="1">
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28" s="1">
         <v>100</v>
       </c>
-      <c r="J22">
+      <c r="H28" s="1">
+        <v>0</v>
+      </c>
+      <c r="I28" s="2">
+        <v>9.5</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" t="s">
+        <v>18</v>
+      </c>
+      <c r="B29" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29" t="s">
+        <v>34</v>
+      </c>
+      <c r="D29">
         <v>32</v>
       </c>
-      <c r="K22" s="1">
+      <c r="E29">
+        <v>32</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29" s="1">
         <v>100</v>
       </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K22"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" customWidth="1"/>
-    <col min="7" max="8" width="9.140625" style="1"/>
-    <col min="9" max="9" width="9.140625" style="2"/>
-    <col min="11" max="11" width="9.140625" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="H29" s="1">
+        <v>0</v>
+      </c>
+      <c r="I29" s="2">
+        <v>9.5</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" t="s">
         <v>18</v>
       </c>
-      <c r="C2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2">
-        <v>43</v>
-      </c>
-      <c r="E2">
-        <v>37</v>
-      </c>
-      <c r="F2">
-        <v>6</v>
-      </c>
-      <c r="G2" s="1">
-        <v>86.05</v>
-      </c>
-      <c r="H2" s="1">
-        <v>13.95</v>
-      </c>
-      <c r="I2" s="2">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3">
-        <v>41</v>
-      </c>
-      <c r="E3">
-        <v>30</v>
-      </c>
-      <c r="F3">
-        <v>11</v>
-      </c>
-      <c r="G3" s="1">
-        <v>73.17</v>
-      </c>
-      <c r="H3" s="1">
-        <v>26.83</v>
-      </c>
-      <c r="I3" s="2">
-        <v>6.7</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4">
-        <v>42</v>
-      </c>
-      <c r="E4">
-        <v>40</v>
-      </c>
-      <c r="F4">
-        <v>2</v>
-      </c>
-      <c r="G4" s="1">
-        <v>95.23999999999999</v>
-      </c>
-      <c r="H4" s="1">
-        <v>4.76</v>
-      </c>
-      <c r="I4" s="2">
-        <v>9</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5">
-        <v>41</v>
-      </c>
-      <c r="E5">
-        <v>38</v>
-      </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5" s="1">
-        <v>92.68000000000001</v>
-      </c>
-      <c r="H5" s="1">
-        <v>7.32</v>
-      </c>
-      <c r="I5" s="2">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6">
-        <v>43</v>
-      </c>
-      <c r="E6">
-        <v>32</v>
-      </c>
-      <c r="F6">
-        <v>11</v>
-      </c>
-      <c r="G6" s="1">
-        <v>74.42</v>
-      </c>
-      <c r="H6" s="1">
-        <v>25.58</v>
-      </c>
-      <c r="I6" s="2">
-        <v>6.7</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7">
-        <v>26</v>
-      </c>
-      <c r="E7">
-        <v>20</v>
-      </c>
-      <c r="F7">
-        <v>6</v>
-      </c>
-      <c r="G7" s="1">
-        <v>76.92</v>
-      </c>
-      <c r="H7" s="1">
-        <v>23.08</v>
-      </c>
-      <c r="I7" s="2">
-        <v>7.5</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="A8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8">
-        <v>43</v>
-      </c>
-      <c r="E8">
-        <v>40</v>
-      </c>
-      <c r="F8">
-        <v>3</v>
-      </c>
-      <c r="G8" s="1">
-        <v>93.02</v>
-      </c>
-      <c r="H8" s="1">
-        <v>6.98</v>
-      </c>
-      <c r="I8" s="2">
-        <v>8.4</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9">
-        <v>41</v>
-      </c>
-      <c r="E9">
-        <v>34</v>
-      </c>
-      <c r="F9">
-        <v>7</v>
-      </c>
-      <c r="G9" s="1">
-        <v>82.93000000000001</v>
-      </c>
-      <c r="H9" s="1">
-        <v>17.07</v>
-      </c>
-      <c r="I9" s="2">
-        <v>7.5</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10">
-        <v>42</v>
-      </c>
-      <c r="E10">
-        <v>39</v>
-      </c>
-      <c r="F10">
-        <v>3</v>
-      </c>
-      <c r="G10" s="1">
-        <v>92.86</v>
-      </c>
-      <c r="H10" s="1">
-        <v>7.14</v>
-      </c>
-      <c r="I10" s="2">
-        <v>8.6</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11">
-        <v>41</v>
-      </c>
-      <c r="E11">
-        <v>38</v>
-      </c>
-      <c r="F11">
-        <v>3</v>
-      </c>
-      <c r="G11" s="1">
-        <v>92.68000000000001</v>
-      </c>
-      <c r="H11" s="1">
-        <v>7.32</v>
-      </c>
-      <c r="I11" s="2">
-        <v>8</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C12" t="s">
-        <v>31</v>
-      </c>
-      <c r="D12">
-        <v>41</v>
-      </c>
-      <c r="E12">
-        <v>37</v>
-      </c>
-      <c r="F12">
-        <v>4</v>
-      </c>
-      <c r="G12" s="1">
-        <v>90.23999999999999</v>
-      </c>
-      <c r="H12" s="1">
-        <v>9.76</v>
-      </c>
-      <c r="I12" s="2">
-        <v>7.5</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" t="s">
-        <v>28</v>
-      </c>
-      <c r="D13">
-        <v>36</v>
-      </c>
-      <c r="E13">
-        <v>24</v>
-      </c>
-      <c r="F13">
-        <v>12</v>
-      </c>
-      <c r="G13" s="1">
-        <v>66.67</v>
-      </c>
-      <c r="H13" s="1">
-        <v>33.33</v>
-      </c>
-      <c r="I13" s="2">
-        <v>6.8</v>
-      </c>
-      <c r="J13">
-        <v>1</v>
-      </c>
-      <c r="K13" s="1">
-        <v>2.78</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" t="s">
-        <v>23</v>
-      </c>
-      <c r="C14" t="s">
-        <v>33</v>
-      </c>
-      <c r="D14">
-        <v>26</v>
-      </c>
-      <c r="E14">
-        <v>25</v>
-      </c>
-      <c r="F14">
-        <v>1</v>
-      </c>
-      <c r="G14" s="1">
-        <v>96.15000000000001</v>
-      </c>
-      <c r="H14" s="1">
-        <v>3.85</v>
-      </c>
-      <c r="I14" s="2">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" t="s">
-        <v>30</v>
-      </c>
-      <c r="D15">
-        <v>43</v>
-      </c>
-      <c r="E15">
-        <v>30</v>
-      </c>
-      <c r="F15">
-        <v>13</v>
-      </c>
-      <c r="G15" s="1">
-        <v>69.77</v>
-      </c>
-      <c r="H15" s="1">
-        <v>30.23</v>
-      </c>
-      <c r="I15" s="2">
-        <v>6.9</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="A16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" t="s">
-        <v>24</v>
-      </c>
-      <c r="C16" t="s">
-        <v>32</v>
-      </c>
-      <c r="D16">
-        <v>36</v>
-      </c>
-      <c r="E16">
-        <v>29</v>
-      </c>
-      <c r="F16">
-        <v>7</v>
-      </c>
-      <c r="G16" s="1">
-        <v>80.56</v>
-      </c>
-      <c r="H16" s="1">
-        <v>19.44</v>
-      </c>
-      <c r="I16" s="2">
-        <v>8.1</v>
-      </c>
-      <c r="J16">
-        <v>1</v>
-      </c>
-      <c r="K16" s="1">
-        <v>2.78</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
-      <c r="A17" t="s">
-        <v>16</v>
-      </c>
-      <c r="B17" t="s">
-        <v>24</v>
-      </c>
-      <c r="C17" t="s">
-        <v>31</v>
-      </c>
-      <c r="D17">
-        <v>36</v>
-      </c>
-      <c r="E17">
-        <v>30</v>
-      </c>
-      <c r="F17">
-        <v>6</v>
-      </c>
-      <c r="G17" s="1">
-        <v>83.33</v>
-      </c>
-      <c r="H17" s="1">
-        <v>16.67</v>
-      </c>
-      <c r="I17" s="2">
-        <v>7.6</v>
-      </c>
-      <c r="J17">
-        <v>1</v>
-      </c>
-      <c r="K17" s="1">
-        <v>2.78</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
-      <c r="A18" t="s">
-        <v>17</v>
-      </c>
-      <c r="B18" t="s">
-        <v>20</v>
-      </c>
-      <c r="C18" t="s">
-        <v>32</v>
-      </c>
-      <c r="D18">
-        <v>42</v>
-      </c>
-      <c r="E18">
-        <v>42</v>
-      </c>
-      <c r="F18">
-        <v>0</v>
-      </c>
-      <c r="G18" s="1">
+      <c r="D30">
+        <v>174</v>
+      </c>
+      <c r="E30">
+        <v>174</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30" s="1">
         <v>100</v>
       </c>
-      <c r="H18" s="1">
-        <v>0</v>
-      </c>
-      <c r="I18" s="2">
-        <v>8.6</v>
-      </c>
-      <c r="J18">
-        <v>0</v>
-      </c>
-      <c r="K18" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
-      <c r="A19" t="s">
-        <v>17</v>
-      </c>
-      <c r="B19" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" t="s">
-        <v>29</v>
-      </c>
-      <c r="D19">
-        <v>34</v>
-      </c>
-      <c r="E19">
-        <v>34</v>
-      </c>
-      <c r="F19">
-        <v>0</v>
-      </c>
-      <c r="G19" s="1">
-        <v>100</v>
-      </c>
-      <c r="H19" s="1">
-        <v>0</v>
-      </c>
-      <c r="I19" s="2">
-        <v>9</v>
-      </c>
-      <c r="J19">
-        <v>0</v>
-      </c>
-      <c r="K19" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
-      <c r="A20" t="s">
-        <v>17</v>
-      </c>
-      <c r="B20" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20" t="s">
-        <v>33</v>
-      </c>
-      <c r="D20">
-        <v>34</v>
-      </c>
-      <c r="E20">
-        <v>34</v>
-      </c>
-      <c r="F20">
-        <v>0</v>
-      </c>
-      <c r="G20" s="1">
-        <v>100</v>
-      </c>
-      <c r="H20" s="1">
-        <v>0</v>
-      </c>
-      <c r="I20" s="2">
-        <v>9</v>
-      </c>
-      <c r="J20">
-        <v>0</v>
-      </c>
-      <c r="K20" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
-      <c r="A21" t="s">
-        <v>17</v>
-      </c>
-      <c r="B21" t="s">
-        <v>26</v>
-      </c>
-      <c r="C21" t="s">
-        <v>29</v>
-      </c>
-      <c r="D21">
-        <v>32</v>
-      </c>
-      <c r="E21">
-        <v>32</v>
-      </c>
-      <c r="F21">
-        <v>0</v>
-      </c>
-      <c r="G21" s="1">
-        <v>100</v>
-      </c>
-      <c r="H21" s="1">
-        <v>0</v>
-      </c>
-      <c r="I21" s="2">
-        <v>9.5</v>
-      </c>
-      <c r="J21">
-        <v>0</v>
-      </c>
-      <c r="K21" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11">
-      <c r="A22" t="s">
-        <v>17</v>
-      </c>
-      <c r="B22" t="s">
-        <v>26</v>
-      </c>
-      <c r="C22" t="s">
-        <v>33</v>
-      </c>
-      <c r="D22">
-        <v>32</v>
-      </c>
-      <c r="E22">
-        <v>32</v>
-      </c>
-      <c r="F22">
-        <v>0</v>
-      </c>
-      <c r="G22" s="1">
-        <v>100</v>
-      </c>
-      <c r="H22" s="1">
-        <v>0</v>
-      </c>
-      <c r="I22" s="2">
-        <v>9.5</v>
-      </c>
-      <c r="J22">
-        <v>0</v>
-      </c>
-      <c r="K22" s="1">
+      <c r="H30" s="1">
+        <v>0</v>
+      </c>
+      <c r="I30" s="2">
+        <v>9.1</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30" s="1">
         <v>0</v>
       </c>
     </row>

--- a/academias/Laboratorio Clínico - Estadisticos 20222.xlsx
+++ b/academias/Laboratorio Clínico - Estadisticos 20222.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="36">
   <si>
     <t>Docente</t>
   </si>
@@ -68,9 +68,6 @@
     <t>Rivera Serra Alma Lilian</t>
   </si>
   <si>
-    <t>Total</t>
-  </si>
-  <si>
     <t>Ángel Martínez Gerson Hermenegildo</t>
   </si>
   <si>
@@ -80,6 +77,9 @@
     <t>REALIZA ANÁLISIS CITOQUÍMICOS A LÍQUIDOS Y SECRECIONES CORPORALES</t>
   </si>
   <si>
+    <t>Totales Docente</t>
+  </si>
+  <si>
     <t>ANALIZA SANGRE CON BASE EN TÉCNICAS DE QUÍMICA CLÍNICA</t>
   </si>
   <si>
@@ -93,6 +93,9 @@
   </si>
   <si>
     <t>ANALIZA SANGRE MEDIANTE PRUEBAS HORMONALES, TOXICOLÓGICAS Y DE MARCADORES TUMORALES</t>
+  </si>
+  <si>
+    <t>Totales Generales</t>
   </si>
   <si>
     <t>2ALCM</t>
@@ -487,7 +490,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="50.7109375" customWidth="1"/>
     <col min="7" max="8" width="9.140625" style="1"/>
     <col min="9" max="9" width="9.140625" style="2"/>
     <col min="11" max="11" width="9.140625" style="1"/>
@@ -533,10 +536,10 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D2">
         <v>43</v>
@@ -568,10 +571,10 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3">
         <v>42</v>
@@ -603,10 +606,10 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D4">
         <v>42</v>
@@ -638,10 +641,10 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D5">
         <v>41</v>
@@ -672,6 +675,9 @@
       <c r="A6" t="s">
         <v>11</v>
       </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
       <c r="D6">
         <v>168</v>
       </c>
@@ -702,10 +708,10 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D7">
         <v>42</v>
@@ -740,7 +746,7 @@
         <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D8">
         <v>26</v>
@@ -771,6 +777,9 @@
       <c r="A9" t="s">
         <v>12</v>
       </c>
+      <c r="B9" t="s">
+        <v>20</v>
+      </c>
       <c r="D9">
         <v>68</v>
       </c>
@@ -804,7 +813,7 @@
         <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D10">
         <v>43</v>
@@ -835,6 +844,9 @@
       <c r="A11" t="s">
         <v>13</v>
       </c>
+      <c r="B11" t="s">
+        <v>20</v>
+      </c>
       <c r="D11">
         <v>43</v>
       </c>
@@ -868,7 +880,7 @@
         <v>22</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D12">
         <v>42</v>
@@ -899,6 +911,9 @@
       <c r="A13" t="s">
         <v>14</v>
       </c>
+      <c r="B13" t="s">
+        <v>20</v>
+      </c>
       <c r="D13">
         <v>42</v>
       </c>
@@ -932,7 +947,7 @@
         <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D14">
         <v>42</v>
@@ -967,7 +982,7 @@
         <v>24</v>
       </c>
       <c r="C15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D15">
         <v>41</v>
@@ -1002,7 +1017,7 @@
         <v>23</v>
       </c>
       <c r="C16" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D16">
         <v>41</v>
@@ -1034,10 +1049,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C17" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D17">
         <v>36</v>
@@ -1072,7 +1087,7 @@
         <v>25</v>
       </c>
       <c r="C18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D18">
         <v>26</v>
@@ -1103,6 +1118,9 @@
       <c r="A19" t="s">
         <v>15</v>
       </c>
+      <c r="B19" t="s">
+        <v>20</v>
+      </c>
       <c r="D19">
         <v>186</v>
       </c>
@@ -1136,7 +1154,7 @@
         <v>22</v>
       </c>
       <c r="C20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D20">
         <v>42</v>
@@ -1171,7 +1189,7 @@
         <v>24</v>
       </c>
       <c r="C21" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D21">
         <v>36</v>
@@ -1206,7 +1224,7 @@
         <v>23</v>
       </c>
       <c r="C22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D22">
         <v>36</v>
@@ -1237,6 +1255,9 @@
       <c r="A23" t="s">
         <v>16</v>
       </c>
+      <c r="B23" t="s">
+        <v>20</v>
+      </c>
       <c r="D23">
         <v>114</v>
       </c>
@@ -1266,46 +1287,52 @@
       <c r="A24" t="s">
         <v>17</v>
       </c>
+      <c r="B24" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" t="s">
+        <v>29</v>
+      </c>
       <c r="D24">
-        <v>795</v>
+        <v>42</v>
       </c>
       <c r="E24">
-        <v>697</v>
+        <v>42</v>
       </c>
       <c r="F24">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="G24" s="1">
-        <v>87.7</v>
+        <v>100</v>
       </c>
       <c r="H24" s="1">
-        <v>12.3</v>
+        <v>0</v>
       </c>
       <c r="I24" s="2">
-        <v>8.1</v>
+        <v>8.6</v>
       </c>
       <c r="J24">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K24" s="1">
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C25" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D25">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="E25">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1317,7 +1344,7 @@
         <v>0</v>
       </c>
       <c r="I25" s="2">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -1328,13 +1355,13 @@
     </row>
     <row r="26" spans="1:11">
       <c r="A26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C26" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D26">
         <v>34</v>
@@ -1363,19 +1390,19 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B27" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C27" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D27">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E27">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -1387,7 +1414,7 @@
         <v>0</v>
       </c>
       <c r="I27" s="2">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -1398,13 +1425,13 @@
     </row>
     <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B28" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C28" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D28">
         <v>32</v>
@@ -1433,19 +1460,16 @@
     </row>
     <row r="29" spans="1:11">
       <c r="A29" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B29" t="s">
-        <v>25</v>
-      </c>
-      <c r="C29" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="D29">
-        <v>32</v>
+        <v>174</v>
       </c>
       <c r="E29">
-        <v>32</v>
+        <v>174</v>
       </c>
       <c r="F29">
         <v>0</v>
@@ -1457,7 +1481,7 @@
         <v>0</v>
       </c>
       <c r="I29" s="2">
-        <v>9.5</v>
+        <v>9.1</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -1467,32 +1491,32 @@
       </c>
     </row>
     <row r="30" spans="1:11">
-      <c r="A30" t="s">
-        <v>18</v>
+      <c r="B30" t="s">
+        <v>26</v>
       </c>
       <c r="D30">
-        <v>174</v>
+        <v>795</v>
       </c>
       <c r="E30">
-        <v>174</v>
+        <v>697</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="G30" s="1">
-        <v>100</v>
+        <v>87.7</v>
       </c>
       <c r="H30" s="1">
-        <v>0</v>
+        <v>12.3</v>
       </c>
       <c r="I30" s="2">
-        <v>9.1</v>
+        <v>8.1</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K30" s="1">
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
   </sheetData>
@@ -1552,10 +1576,10 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D2">
         <v>43</v>
@@ -1587,10 +1611,10 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3">
         <v>42</v>
@@ -1622,10 +1646,10 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D4">
         <v>42</v>
@@ -1657,10 +1681,10 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D5">
         <v>41</v>
@@ -1691,6 +1715,9 @@
       <c r="A6" t="s">
         <v>11</v>
       </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
       <c r="D6">
         <v>168</v>
       </c>
@@ -1721,10 +1748,10 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D7">
         <v>42</v>
@@ -1759,7 +1786,7 @@
         <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D8">
         <v>26</v>
@@ -1790,6 +1817,9 @@
       <c r="A9" t="s">
         <v>12</v>
       </c>
+      <c r="B9" t="s">
+        <v>20</v>
+      </c>
       <c r="D9">
         <v>68</v>
       </c>
@@ -1823,7 +1853,7 @@
         <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D10">
         <v>43</v>
@@ -1854,6 +1884,9 @@
       <c r="A11" t="s">
         <v>13</v>
       </c>
+      <c r="B11" t="s">
+        <v>20</v>
+      </c>
       <c r="D11">
         <v>43</v>
       </c>
@@ -1887,7 +1920,7 @@
         <v>22</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D12">
         <v>42</v>
@@ -1918,6 +1951,9 @@
       <c r="A13" t="s">
         <v>14</v>
       </c>
+      <c r="B13" t="s">
+        <v>20</v>
+      </c>
       <c r="D13">
         <v>42</v>
       </c>
@@ -1951,7 +1987,7 @@
         <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D14">
         <v>42</v>
@@ -1986,7 +2022,7 @@
         <v>24</v>
       </c>
       <c r="C15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D15">
         <v>41</v>
@@ -2021,7 +2057,7 @@
         <v>23</v>
       </c>
       <c r="C16" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D16">
         <v>41</v>
@@ -2053,10 +2089,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C17" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D17">
         <v>36</v>
@@ -2091,7 +2127,7 @@
         <v>25</v>
       </c>
       <c r="C18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D18">
         <v>26</v>
@@ -2122,6 +2158,9 @@
       <c r="A19" t="s">
         <v>15</v>
       </c>
+      <c r="B19" t="s">
+        <v>20</v>
+      </c>
       <c r="D19">
         <v>186</v>
       </c>
@@ -2155,7 +2194,7 @@
         <v>22</v>
       </c>
       <c r="C20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D20">
         <v>42</v>
@@ -2190,7 +2229,7 @@
         <v>24</v>
       </c>
       <c r="C21" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D21">
         <v>36</v>
@@ -2225,7 +2264,7 @@
         <v>23</v>
       </c>
       <c r="C22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D22">
         <v>36</v>
@@ -2256,6 +2295,9 @@
       <c r="A23" t="s">
         <v>16</v>
       </c>
+      <c r="B23" t="s">
+        <v>20</v>
+      </c>
       <c r="D23">
         <v>114</v>
       </c>
@@ -2285,46 +2327,52 @@
       <c r="A24" t="s">
         <v>17</v>
       </c>
+      <c r="B24" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" t="s">
+        <v>29</v>
+      </c>
       <c r="D24">
-        <v>795</v>
+        <v>42</v>
       </c>
       <c r="E24">
-        <v>697</v>
+        <v>42</v>
       </c>
       <c r="F24">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="G24" s="1">
-        <v>87.7</v>
+        <v>100</v>
       </c>
       <c r="H24" s="1">
-        <v>12.3</v>
+        <v>0</v>
       </c>
       <c r="I24" s="2">
-        <v>8.1</v>
+        <v>8.6</v>
       </c>
       <c r="J24">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K24" s="1">
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C25" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D25">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="E25">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -2336,7 +2384,7 @@
         <v>0</v>
       </c>
       <c r="I25" s="2">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -2347,13 +2395,13 @@
     </row>
     <row r="26" spans="1:11">
       <c r="A26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C26" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D26">
         <v>34</v>
@@ -2382,19 +2430,19 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B27" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C27" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D27">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E27">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -2406,7 +2454,7 @@
         <v>0</v>
       </c>
       <c r="I27" s="2">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -2417,13 +2465,13 @@
     </row>
     <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B28" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C28" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D28">
         <v>32</v>
@@ -2452,19 +2500,16 @@
     </row>
     <row r="29" spans="1:11">
       <c r="A29" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B29" t="s">
-        <v>25</v>
-      </c>
-      <c r="C29" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="D29">
-        <v>32</v>
+        <v>174</v>
       </c>
       <c r="E29">
-        <v>32</v>
+        <v>174</v>
       </c>
       <c r="F29">
         <v>0</v>
@@ -2476,7 +2521,7 @@
         <v>0</v>
       </c>
       <c r="I29" s="2">
-        <v>9.5</v>
+        <v>9.1</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -2486,32 +2531,32 @@
       </c>
     </row>
     <row r="30" spans="1:11">
-      <c r="A30" t="s">
-        <v>18</v>
+      <c r="B30" t="s">
+        <v>26</v>
       </c>
       <c r="D30">
-        <v>174</v>
+        <v>795</v>
       </c>
       <c r="E30">
-        <v>174</v>
+        <v>697</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="G30" s="1">
-        <v>100</v>
+        <v>87.7</v>
       </c>
       <c r="H30" s="1">
-        <v>0</v>
+        <v>12.3</v>
       </c>
       <c r="I30" s="2">
-        <v>9.1</v>
+        <v>8.1</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K30" s="1">
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Laboratorio Clínico - Estadisticos 20222.xlsx
+++ b/academias/Laboratorio Clínico - Estadisticos 20222.xlsx
@@ -8,14 +8,15 @@
   </bookViews>
   <sheets>
     <sheet name="1er Parcial" sheetId="1" r:id="rId1"/>
-    <sheet name="Final" sheetId="2" r:id="rId2"/>
+    <sheet name="2o Parcial" sheetId="2" r:id="rId2"/>
+    <sheet name="Final" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="36">
   <si>
     <t>Docente</t>
   </si>
@@ -1585,6 +1586,1046 @@
         <v>43</v>
       </c>
       <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>43</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0</v>
+      </c>
+      <c r="H2" s="1">
+        <v>100</v>
+      </c>
+      <c r="I2" s="2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>43</v>
+      </c>
+      <c r="K2" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3">
+        <v>42</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>42</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0</v>
+      </c>
+      <c r="H3" s="1">
+        <v>100</v>
+      </c>
+      <c r="I3" s="2">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>42</v>
+      </c>
+      <c r="K3" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4">
+        <v>42</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>42</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1">
+        <v>100</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>42</v>
+      </c>
+      <c r="K4" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5">
+        <v>41</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>41</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0</v>
+      </c>
+      <c r="H5" s="1">
+        <v>100</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>41</v>
+      </c>
+      <c r="K5" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6">
+        <v>168</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>168</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
+        <v>100</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>168</v>
+      </c>
+      <c r="K6" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7">
+        <v>42</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>42</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
+        <v>100</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>42</v>
+      </c>
+      <c r="K7" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8">
+        <v>26</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>26</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1">
+        <v>100</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>26</v>
+      </c>
+      <c r="K8" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9">
+        <v>68</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>68</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1">
+        <v>100</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>68</v>
+      </c>
+      <c r="K9" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10">
+        <v>43</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>43</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1">
+        <v>100</v>
+      </c>
+      <c r="I10" s="2">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>43</v>
+      </c>
+      <c r="K10" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11">
+        <v>43</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>43</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1">
+        <v>100</v>
+      </c>
+      <c r="I11" s="2">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>43</v>
+      </c>
+      <c r="K11" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12">
+        <v>42</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>42</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1">
+        <v>100</v>
+      </c>
+      <c r="I12" s="2">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>42</v>
+      </c>
+      <c r="K12" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13">
+        <v>42</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>42</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1">
+        <v>100</v>
+      </c>
+      <c r="I13" s="2">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>42</v>
+      </c>
+      <c r="K13" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14">
+        <v>42</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>42</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1">
+        <v>100</v>
+      </c>
+      <c r="I14" s="2">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>42</v>
+      </c>
+      <c r="K14" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15">
+        <v>41</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>41</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1">
+        <v>100</v>
+      </c>
+      <c r="I15" s="2">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>41</v>
+      </c>
+      <c r="K15" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16">
+        <v>41</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>41</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1">
+        <v>100</v>
+      </c>
+      <c r="I16" s="2">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>41</v>
+      </c>
+      <c r="K16" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" t="s">
+        <v>33</v>
+      </c>
+      <c r="D17">
+        <v>36</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>36</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1">
+        <v>100</v>
+      </c>
+      <c r="I17" s="2">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>36</v>
+      </c>
+      <c r="K17" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18">
+        <v>26</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>26</v>
+      </c>
+      <c r="G18" s="1">
+        <v>0</v>
+      </c>
+      <c r="H18" s="1">
+        <v>100</v>
+      </c>
+      <c r="I18" s="2">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>26</v>
+      </c>
+      <c r="K18" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19">
+        <v>186</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>186</v>
+      </c>
+      <c r="G19" s="1">
+        <v>0</v>
+      </c>
+      <c r="H19" s="1">
+        <v>100</v>
+      </c>
+      <c r="I19" s="2">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>186</v>
+      </c>
+      <c r="K19" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" t="s">
+        <v>31</v>
+      </c>
+      <c r="D20">
+        <v>42</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>42</v>
+      </c>
+      <c r="G20" s="1">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1">
+        <v>100</v>
+      </c>
+      <c r="I20" s="2">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>42</v>
+      </c>
+      <c r="K20" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" t="s">
+        <v>33</v>
+      </c>
+      <c r="D21">
+        <v>36</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>36</v>
+      </c>
+      <c r="G21" s="1">
+        <v>0</v>
+      </c>
+      <c r="H21" s="1">
+        <v>100</v>
+      </c>
+      <c r="I21" s="2">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>36</v>
+      </c>
+      <c r="K21" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22" t="s">
+        <v>23</v>
+      </c>
+      <c r="C22" t="s">
+        <v>33</v>
+      </c>
+      <c r="D22">
+        <v>36</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>36</v>
+      </c>
+      <c r="G22" s="1">
+        <v>0</v>
+      </c>
+      <c r="H22" s="1">
+        <v>100</v>
+      </c>
+      <c r="I22" s="2">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>36</v>
+      </c>
+      <c r="K22" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" t="s">
+        <v>16</v>
+      </c>
+      <c r="B23" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23">
+        <v>114</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>114</v>
+      </c>
+      <c r="G23" s="1">
+        <v>0</v>
+      </c>
+      <c r="H23" s="1">
+        <v>100</v>
+      </c>
+      <c r="I23" s="2">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>114</v>
+      </c>
+      <c r="K23" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" t="s">
+        <v>17</v>
+      </c>
+      <c r="B24" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" t="s">
+        <v>29</v>
+      </c>
+      <c r="D24">
+        <v>42</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>42</v>
+      </c>
+      <c r="G24" s="1">
+        <v>0</v>
+      </c>
+      <c r="H24" s="1">
+        <v>100</v>
+      </c>
+      <c r="I24" s="2">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>42</v>
+      </c>
+      <c r="K24" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" t="s">
+        <v>17</v>
+      </c>
+      <c r="B25" t="s">
+        <v>21</v>
+      </c>
+      <c r="C25" t="s">
+        <v>34</v>
+      </c>
+      <c r="D25">
+        <v>34</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>34</v>
+      </c>
+      <c r="G25" s="1">
+        <v>0</v>
+      </c>
+      <c r="H25" s="1">
+        <v>100</v>
+      </c>
+      <c r="I25" s="2">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>34</v>
+      </c>
+      <c r="K25" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" t="s">
+        <v>17</v>
+      </c>
+      <c r="B26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C26" t="s">
+        <v>34</v>
+      </c>
+      <c r="D26">
+        <v>34</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>34</v>
+      </c>
+      <c r="G26" s="1">
+        <v>0</v>
+      </c>
+      <c r="H26" s="1">
+        <v>100</v>
+      </c>
+      <c r="I26" s="2">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>34</v>
+      </c>
+      <c r="K26" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" t="s">
+        <v>17</v>
+      </c>
+      <c r="B27" t="s">
+        <v>21</v>
+      </c>
+      <c r="C27" t="s">
+        <v>35</v>
+      </c>
+      <c r="D27">
+        <v>32</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>32</v>
+      </c>
+      <c r="G27" s="1">
+        <v>0</v>
+      </c>
+      <c r="H27" s="1">
+        <v>100</v>
+      </c>
+      <c r="I27" s="2">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>32</v>
+      </c>
+      <c r="K27" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" t="s">
+        <v>17</v>
+      </c>
+      <c r="B28" t="s">
+        <v>25</v>
+      </c>
+      <c r="C28" t="s">
+        <v>35</v>
+      </c>
+      <c r="D28">
+        <v>32</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>32</v>
+      </c>
+      <c r="G28" s="1">
+        <v>0</v>
+      </c>
+      <c r="H28" s="1">
+        <v>100</v>
+      </c>
+      <c r="I28" s="2">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>32</v>
+      </c>
+      <c r="K28" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" t="s">
+        <v>17</v>
+      </c>
+      <c r="B29" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29">
+        <v>174</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>174</v>
+      </c>
+      <c r="G29" s="1">
+        <v>0</v>
+      </c>
+      <c r="H29" s="1">
+        <v>100</v>
+      </c>
+      <c r="I29" s="2">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>174</v>
+      </c>
+      <c r="K29" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="B30" t="s">
+        <v>26</v>
+      </c>
+      <c r="D30">
+        <v>795</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>795</v>
+      </c>
+      <c r="G30" s="1">
+        <v>0</v>
+      </c>
+      <c r="H30" s="1">
+        <v>100</v>
+      </c>
+      <c r="I30" s="2">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>795</v>
+      </c>
+      <c r="K30" s="1">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K30"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="7" max="8" width="9.140625" style="1"/>
+    <col min="9" max="9" width="9.140625" style="2"/>
+    <col min="11" max="11" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2">
+        <v>43</v>
+      </c>
+      <c r="E2">
         <v>37</v>
       </c>
       <c r="F2">

--- a/academias/Laboratorio Clínico - Estadisticos 20222.xlsx
+++ b/academias/Laboratorio Clínico - Estadisticos 20222.xlsx
@@ -1059,25 +1059,25 @@
         <v>36</v>
       </c>
       <c r="E17">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F17">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G17" s="1">
-        <v>66.7</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="H17" s="1">
-        <v>33.3</v>
+        <v>30.6</v>
       </c>
       <c r="I17" s="2">
-        <v>7.3</v>
+        <v>6.9</v>
       </c>
       <c r="J17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1126,25 +1126,25 @@
         <v>186</v>
       </c>
       <c r="E19">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F19">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G19" s="1">
-        <v>87.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="H19" s="1">
-        <v>12.4</v>
+        <v>11.8</v>
       </c>
       <c r="I19" s="2">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="J19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1499,25 +1499,25 @@
         <v>795</v>
       </c>
       <c r="E30">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="F30">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G30" s="1">
-        <v>87.7</v>
+        <v>87.8</v>
       </c>
       <c r="H30" s="1">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="I30" s="2">
         <v>8.1</v>
       </c>
       <c r="J30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K30" s="1">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
   </sheetData>
@@ -1586,25 +1586,25 @@
         <v>43</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F2">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>14</v>
       </c>
       <c r="I2" s="2">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="J2">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1621,25 +1621,25 @@
         <v>42</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F3">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>28.6</v>
       </c>
       <c r="I3" s="2">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="J3">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1656,25 +1656,25 @@
         <v>42</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F4">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>2.4</v>
       </c>
       <c r="I4" s="2">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J4">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1691,25 +1691,25 @@
         <v>41</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F5">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>92.7</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>7.3</v>
       </c>
       <c r="I5" s="2">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="J5">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1723,25 +1723,25 @@
         <v>168</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="F6">
-        <v>168</v>
+        <v>22</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>13.1</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J6">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1994,25 +1994,25 @@
         <v>42</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F14">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>2.4</v>
       </c>
       <c r="I14" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J14">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -2029,25 +2029,25 @@
         <v>41</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F15">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>90.2</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I15" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J15">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2064,25 +2064,25 @@
         <v>41</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F16">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>92.7</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>7.3</v>
       </c>
       <c r="I16" s="2">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J16">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -2099,25 +2099,25 @@
         <v>36</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F17">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="H17" s="1">
-        <v>100</v>
+        <v>13.9</v>
       </c>
       <c r="I17" s="2">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J17">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -2134,25 +2134,25 @@
         <v>26</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F18">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>96.2</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>3.8</v>
       </c>
       <c r="I18" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J18">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -2166,25 +2166,25 @@
         <v>186</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="F19">
-        <v>186</v>
+        <v>14</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="H19" s="1">
-        <v>100</v>
+        <v>7.5</v>
       </c>
       <c r="I19" s="2">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J19">
-        <v>186</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -2338,25 +2338,25 @@
         <v>42</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="F24">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G24" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H24" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I24" s="2">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J24">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K24" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -2373,25 +2373,25 @@
         <v>34</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F25">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="G25" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H25" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I25" s="2">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J25">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K25" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -2408,25 +2408,25 @@
         <v>34</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F26">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="G26" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H26" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I26" s="2">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J26">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K26" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -2443,25 +2443,25 @@
         <v>32</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F27">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G27" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H27" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I27" s="2">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="J27">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K27" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -2478,25 +2478,25 @@
         <v>32</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F28">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G28" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H28" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I28" s="2">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="J28">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K28" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -2510,25 +2510,25 @@
         <v>174</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>174</v>
       </c>
       <c r="F29">
-        <v>174</v>
+        <v>0</v>
       </c>
       <c r="G29" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H29" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I29" s="2">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J29">
-        <v>174</v>
+        <v>0</v>
       </c>
       <c r="K29" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -2539,25 +2539,25 @@
         <v>795</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>492</v>
       </c>
       <c r="F30">
-        <v>795</v>
+        <v>303</v>
       </c>
       <c r="G30" s="1">
-        <v>0</v>
+        <v>61.9</v>
       </c>
       <c r="H30" s="1">
-        <v>100</v>
+        <v>38.1</v>
       </c>
       <c r="I30" s="2">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="J30">
-        <v>795</v>
+        <v>267</v>
       </c>
       <c r="K30" s="1">
-        <v>100</v>
+        <v>33.6</v>
       </c>
     </row>
   </sheetData>
@@ -2638,7 +2638,7 @@
         <v>14</v>
       </c>
       <c r="I2" s="2">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -2661,19 +2661,19 @@
         <v>42</v>
       </c>
       <c r="E3">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G3" s="1">
-        <v>73.8</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="H3" s="1">
-        <v>26.2</v>
+        <v>28.6</v>
       </c>
       <c r="I3" s="2">
-        <v>6.7</v>
+        <v>7.1</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -2696,19 +2696,19 @@
         <v>42</v>
       </c>
       <c r="E4">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" s="1">
-        <v>95.2</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="H4" s="1">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="I4" s="2">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -2743,7 +2743,7 @@
         <v>7.3</v>
       </c>
       <c r="I5" s="2">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -3034,19 +3034,19 @@
         <v>42</v>
       </c>
       <c r="E14">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G14" s="1">
-        <v>92.90000000000001</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="H14" s="1">
-        <v>7.1</v>
+        <v>2.4</v>
       </c>
       <c r="I14" s="2">
-        <v>8.6</v>
+        <v>8.9</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -3069,19 +3069,19 @@
         <v>41</v>
       </c>
       <c r="E15">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G15" s="1">
-        <v>92.7</v>
+        <v>90.2</v>
       </c>
       <c r="H15" s="1">
-        <v>7.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I15" s="2">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -3104,19 +3104,19 @@
         <v>41</v>
       </c>
       <c r="E16">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G16" s="1">
-        <v>90.2</v>
+        <v>92.7</v>
       </c>
       <c r="H16" s="1">
-        <v>9.800000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="I16" s="2">
-        <v>7.5</v>
+        <v>7.9</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -3139,25 +3139,25 @@
         <v>36</v>
       </c>
       <c r="E17">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F17">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G17" s="1">
-        <v>66.7</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="H17" s="1">
-        <v>33.3</v>
+        <v>13.9</v>
       </c>
       <c r="I17" s="2">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="J17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -3186,7 +3186,7 @@
         <v>3.8</v>
       </c>
       <c r="I18" s="2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -3206,25 +3206,25 @@
         <v>186</v>
       </c>
       <c r="E19">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="F19">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="G19" s="1">
-        <v>87.59999999999999</v>
+        <v>92.5</v>
       </c>
       <c r="H19" s="1">
-        <v>12.4</v>
+        <v>7.5</v>
       </c>
       <c r="I19" s="2">
-        <v>7.9</v>
+        <v>8.4</v>
       </c>
       <c r="J19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -3390,7 +3390,7 @@
         <v>0</v>
       </c>
       <c r="I24" s="2">
-        <v>8.6</v>
+        <v>8.9</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="I25" s="2">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -3460,7 +3460,7 @@
         <v>0</v>
       </c>
       <c r="I26" s="2">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -3495,7 +3495,7 @@
         <v>0</v>
       </c>
       <c r="I27" s="2">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -3530,7 +3530,7 @@
         <v>0</v>
       </c>
       <c r="I28" s="2">
-        <v>9.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -3562,7 +3562,7 @@
         <v>0</v>
       </c>
       <c r="I29" s="2">
-        <v>9.1</v>
+        <v>9.4</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -3579,25 +3579,25 @@
         <v>795</v>
       </c>
       <c r="E30">
-        <v>697</v>
+        <v>706</v>
       </c>
       <c r="F30">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="G30" s="1">
-        <v>87.7</v>
+        <v>88.8</v>
       </c>
       <c r="H30" s="1">
-        <v>12.3</v>
+        <v>11.2</v>
       </c>
       <c r="I30" s="2">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K30" s="1">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Laboratorio Clínico - Estadisticos 20222.xlsx
+++ b/academias/Laboratorio Clínico - Estadisticos 20222.xlsx
@@ -1758,25 +1758,25 @@
         <v>42</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F7">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>31</v>
       </c>
       <c r="I7" s="2">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="J7">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1793,25 +1793,25 @@
         <v>26</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F8">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>15.4</v>
       </c>
       <c r="I8" s="2">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="J8">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1825,25 +1825,25 @@
         <v>68</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="F9">
-        <v>68</v>
+        <v>17</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="I9" s="2">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="J9">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1927,25 +1927,25 @@
         <v>42</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F12">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>16.7</v>
       </c>
       <c r="I12" s="2">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="J12">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1959,25 +1959,25 @@
         <v>42</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F13">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>16.7</v>
       </c>
       <c r="I13" s="2">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="J13">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -2539,25 +2539,25 @@
         <v>795</v>
       </c>
       <c r="E30">
-        <v>492</v>
+        <v>578</v>
       </c>
       <c r="F30">
-        <v>303</v>
+        <v>217</v>
       </c>
       <c r="G30" s="1">
-        <v>61.9</v>
+        <v>72.7</v>
       </c>
       <c r="H30" s="1">
-        <v>38.1</v>
+        <v>27.3</v>
       </c>
       <c r="I30" s="2">
-        <v>5.8</v>
+        <v>6.9</v>
       </c>
       <c r="J30">
-        <v>267</v>
+        <v>157</v>
       </c>
       <c r="K30" s="1">
-        <v>33.6</v>
+        <v>19.7</v>
       </c>
     </row>
   </sheetData>
@@ -2798,19 +2798,19 @@
         <v>42</v>
       </c>
       <c r="E7">
+        <v>29</v>
+      </c>
+      <c r="F7">
+        <v>13</v>
+      </c>
+      <c r="G7" s="1">
+        <v>69</v>
+      </c>
+      <c r="H7" s="1">
         <v>31</v>
       </c>
-      <c r="F7">
-        <v>11</v>
-      </c>
-      <c r="G7" s="1">
-        <v>73.8</v>
-      </c>
-      <c r="H7" s="1">
-        <v>26.2</v>
-      </c>
       <c r="I7" s="2">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -2833,19 +2833,19 @@
         <v>26</v>
       </c>
       <c r="E8">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F8">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G8" s="1">
-        <v>76.90000000000001</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="H8" s="1">
-        <v>23.1</v>
+        <v>15.4</v>
       </c>
       <c r="I8" s="2">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -2877,7 +2877,7 @@
         <v>25</v>
       </c>
       <c r="I9" s="2">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2979,7 +2979,7 @@
         <v>16.7</v>
       </c>
       <c r="I12" s="2">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -3011,7 +3011,7 @@
         <v>16.7</v>
       </c>
       <c r="I13" s="2">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="J13">
         <v>0</v>

--- a/academias/Laboratorio Clínico - Estadisticos 20222.xlsx
+++ b/academias/Laboratorio Clínico - Estadisticos 20222.xlsx
@@ -1196,25 +1196,25 @@
         <v>36</v>
       </c>
       <c r="E21">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G21" s="1">
-        <v>80.59999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="H21" s="1">
-        <v>19.4</v>
+        <v>16.7</v>
       </c>
       <c r="I21" s="2">
         <v>8.1</v>
       </c>
       <c r="J21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -1231,25 +1231,25 @@
         <v>36</v>
       </c>
       <c r="E22">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G22" s="1">
-        <v>83.3</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="H22" s="1">
-        <v>16.7</v>
+        <v>13.9</v>
       </c>
       <c r="I22" s="2">
         <v>7.6</v>
       </c>
       <c r="J22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -1263,25 +1263,25 @@
         <v>114</v>
       </c>
       <c r="E23">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F23">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G23" s="1">
-        <v>77.2</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="H23" s="1">
-        <v>22.8</v>
+        <v>21.1</v>
       </c>
       <c r="I23" s="2">
         <v>7.5</v>
       </c>
       <c r="J23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1">
-        <v>1.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -1499,25 +1499,25 @@
         <v>795</v>
       </c>
       <c r="E30">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="F30">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G30" s="1">
-        <v>87.8</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="H30" s="1">
-        <v>12.2</v>
+        <v>11.9</v>
       </c>
       <c r="I30" s="2">
         <v>8.1</v>
       </c>
       <c r="J30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K30" s="1">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1860,25 +1860,25 @@
         <v>43</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F10">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>7</v>
       </c>
       <c r="I10" s="2">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="J10">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1892,25 +1892,25 @@
         <v>43</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F11">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>7</v>
       </c>
       <c r="I11" s="2">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="J11">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -2201,25 +2201,25 @@
         <v>42</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F20">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="H20" s="1">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="I20" s="2">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="J20">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -2236,25 +2236,25 @@
         <v>36</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F21">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="G21" s="1">
-        <v>0</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="H21" s="1">
-        <v>100</v>
+        <v>11.1</v>
       </c>
       <c r="I21" s="2">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="J21">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -2271,25 +2271,25 @@
         <v>36</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F22">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="G22" s="1">
-        <v>0</v>
+        <v>91.7</v>
       </c>
       <c r="H22" s="1">
-        <v>100</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I22" s="2">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="J22">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -2303,25 +2303,25 @@
         <v>114</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="F23">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="G23" s="1">
-        <v>0</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="H23" s="1">
-        <v>100</v>
+        <v>18.4</v>
       </c>
       <c r="I23" s="2">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="J23">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -2539,25 +2539,25 @@
         <v>795</v>
       </c>
       <c r="E30">
-        <v>578</v>
+        <v>711</v>
       </c>
       <c r="F30">
-        <v>217</v>
+        <v>84</v>
       </c>
       <c r="G30" s="1">
-        <v>72.7</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="H30" s="1">
-        <v>27.3</v>
+        <v>10.6</v>
       </c>
       <c r="I30" s="2">
-        <v>6.9</v>
+        <v>8.4</v>
       </c>
       <c r="J30">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="K30" s="1">
-        <v>19.7</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2912,7 +2912,7 @@
         <v>7</v>
       </c>
       <c r="I10" s="2">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2944,7 +2944,7 @@
         <v>7</v>
       </c>
       <c r="I11" s="2">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -3241,16 +3241,16 @@
         <v>42</v>
       </c>
       <c r="E20">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F20">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G20" s="1">
-        <v>69</v>
+        <v>66.7</v>
       </c>
       <c r="H20" s="1">
-        <v>31</v>
+        <v>33.3</v>
       </c>
       <c r="I20" s="2">
         <v>6.9</v>
@@ -3276,25 +3276,25 @@
         <v>36</v>
       </c>
       <c r="E21">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F21">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G21" s="1">
-        <v>80.59999999999999</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="H21" s="1">
-        <v>19.4</v>
+        <v>11.1</v>
       </c>
       <c r="I21" s="2">
-        <v>8.1</v>
+        <v>8.5</v>
       </c>
       <c r="J21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -3311,25 +3311,25 @@
         <v>36</v>
       </c>
       <c r="E22">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F22">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G22" s="1">
-        <v>83.3</v>
+        <v>91.7</v>
       </c>
       <c r="H22" s="1">
-        <v>16.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I22" s="2">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -3343,25 +3343,25 @@
         <v>114</v>
       </c>
       <c r="E23">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="F23">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G23" s="1">
-        <v>77.2</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="H23" s="1">
-        <v>22.8</v>
+        <v>18.4</v>
       </c>
       <c r="I23" s="2">
-        <v>7.5</v>
+        <v>7.9</v>
       </c>
       <c r="J23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1">
-        <v>1.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -3579,25 +3579,25 @@
         <v>795</v>
       </c>
       <c r="E30">
-        <v>706</v>
+        <v>711</v>
       </c>
       <c r="F30">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="G30" s="1">
-        <v>88.8</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="H30" s="1">
-        <v>11.2</v>
+        <v>10.6</v>
       </c>
       <c r="I30" s="2">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K30" s="1">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Laboratorio Clínico - Estadisticos 20222.xlsx
+++ b/academias/Laboratorio Clínico - Estadisticos 20222.xlsx
@@ -1530,8 +1530,7 @@
   <dimension ref="A1:K30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="1" max="2" width="30.7109375" customWidth="1"/>
     <col min="7" max="8" width="9.140625" style="1"/>
     <col min="9" max="9" width="9.140625" style="2"/>
     <col min="11" max="11" width="9.140625" style="1"/>
@@ -2570,8 +2569,7 @@
   <dimension ref="A1:K30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="1" max="2" width="30.7109375" customWidth="1"/>
     <col min="7" max="8" width="9.140625" style="1"/>
     <col min="9" max="9" width="9.140625" style="2"/>
     <col min="11" max="11" width="9.140625" style="1"/>
@@ -2626,19 +2624,19 @@
         <v>43</v>
       </c>
       <c r="E2">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G2" s="1">
-        <v>86</v>
+        <v>95.3</v>
       </c>
       <c r="H2" s="1">
-        <v>14</v>
+        <v>4.7</v>
       </c>
       <c r="I2" s="2">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -2661,19 +2659,19 @@
         <v>42</v>
       </c>
       <c r="E3">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F3">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G3" s="1">
-        <v>71.40000000000001</v>
+        <v>81</v>
       </c>
       <c r="H3" s="1">
-        <v>28.6</v>
+        <v>19</v>
       </c>
       <c r="I3" s="2">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -2763,19 +2761,19 @@
         <v>168</v>
       </c>
       <c r="E6">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="F6">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G6" s="1">
-        <v>86.90000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="H6" s="1">
-        <v>13.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I6" s="2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -2798,19 +2796,19 @@
         <v>42</v>
       </c>
       <c r="E7">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="F7">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="G7" s="1">
-        <v>69</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H7" s="1">
-        <v>31</v>
+        <v>7.1</v>
       </c>
       <c r="I7" s="2">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -2833,19 +2831,19 @@
         <v>26</v>
       </c>
       <c r="E8">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G8" s="1">
-        <v>84.59999999999999</v>
+        <v>96.2</v>
       </c>
       <c r="H8" s="1">
-        <v>15.4</v>
+        <v>3.8</v>
       </c>
       <c r="I8" s="2">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -2865,19 +2863,19 @@
         <v>68</v>
       </c>
       <c r="E9">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="F9">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="G9" s="1">
-        <v>75</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="H9" s="1">
-        <v>25</v>
+        <v>5.9</v>
       </c>
       <c r="I9" s="2">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -3069,19 +3067,19 @@
         <v>41</v>
       </c>
       <c r="E15">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F15">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G15" s="1">
-        <v>90.2</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="H15" s="1">
-        <v>9.800000000000001</v>
+        <v>17.1</v>
       </c>
       <c r="I15" s="2">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -3104,19 +3102,19 @@
         <v>41</v>
       </c>
       <c r="E16">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F16">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G16" s="1">
-        <v>92.7</v>
+        <v>78</v>
       </c>
       <c r="H16" s="1">
-        <v>7.3</v>
+        <v>22</v>
       </c>
       <c r="I16" s="2">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -3139,19 +3137,19 @@
         <v>36</v>
       </c>
       <c r="E17">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F17">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G17" s="1">
-        <v>86.09999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="H17" s="1">
-        <v>13.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I17" s="2">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -3174,19 +3172,19 @@
         <v>26</v>
       </c>
       <c r="E18">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G18" s="1">
-        <v>96.2</v>
+        <v>92.3</v>
       </c>
       <c r="H18" s="1">
-        <v>3.8</v>
+        <v>7.7</v>
       </c>
       <c r="I18" s="2">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -3206,19 +3204,19 @@
         <v>186</v>
       </c>
       <c r="E19">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="F19">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="G19" s="1">
-        <v>92.5</v>
+        <v>88.2</v>
       </c>
       <c r="H19" s="1">
-        <v>7.5</v>
+        <v>11.8</v>
       </c>
       <c r="I19" s="2">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -3390,7 +3388,7 @@
         <v>0</v>
       </c>
       <c r="I24" s="2">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -3530,7 +3528,7 @@
         <v>0</v>
       </c>
       <c r="I28" s="2">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -3579,16 +3577,16 @@
         <v>795</v>
       </c>
       <c r="E30">
-        <v>711</v>
+        <v>724</v>
       </c>
       <c r="F30">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="G30" s="1">
-        <v>89.40000000000001</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="H30" s="1">
-        <v>10.6</v>
+        <v>8.9</v>
       </c>
       <c r="I30" s="2">
         <v>8.4</v>

--- a/academias/Laboratorio Clínico - Estadisticos 20222.xlsx
+++ b/academias/Laboratorio Clínico - Estadisticos 20222.xlsx
@@ -2965,19 +2965,19 @@
         <v>42</v>
       </c>
       <c r="E12">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G12" s="1">
-        <v>83.3</v>
+        <v>85.7</v>
       </c>
       <c r="H12" s="1">
-        <v>16.7</v>
+        <v>14.3</v>
       </c>
       <c r="I12" s="2">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2997,19 +2997,19 @@
         <v>42</v>
       </c>
       <c r="E13">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G13" s="1">
-        <v>83.3</v>
+        <v>85.7</v>
       </c>
       <c r="H13" s="1">
-        <v>16.7</v>
+        <v>14.3</v>
       </c>
       <c r="I13" s="2">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -3577,16 +3577,16 @@
         <v>795</v>
       </c>
       <c r="E30">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="F30">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G30" s="1">
-        <v>91.09999999999999</v>
+        <v>91.2</v>
       </c>
       <c r="H30" s="1">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I30" s="2">
         <v>8.4</v>

--- a/academias/Laboratorio Clínico - Estadisticos 20222.xlsx
+++ b/academias/Laboratorio Clínico - Estadisticos 20222.xlsx
@@ -2694,19 +2694,19 @@
         <v>42</v>
       </c>
       <c r="E4">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4" s="1">
-        <v>97.59999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="H4" s="1">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="I4" s="2">
-        <v>9.1</v>
+        <v>8.5</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -2729,19 +2729,19 @@
         <v>41</v>
       </c>
       <c r="E5">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G5" s="1">
-        <v>92.7</v>
+        <v>87.8</v>
       </c>
       <c r="H5" s="1">
-        <v>7.3</v>
+        <v>12.2</v>
       </c>
       <c r="I5" s="2">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -2761,19 +2761,19 @@
         <v>168</v>
       </c>
       <c r="E6">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F6">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G6" s="1">
-        <v>91.7</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="H6" s="1">
-        <v>8.300000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="I6" s="2">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -3239,19 +3239,19 @@
         <v>42</v>
       </c>
       <c r="E20">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F20">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="G20" s="1">
-        <v>66.7</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H20" s="1">
-        <v>33.3</v>
+        <v>7.1</v>
       </c>
       <c r="I20" s="2">
-        <v>6.9</v>
+        <v>7.3</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -3274,19 +3274,19 @@
         <v>36</v>
       </c>
       <c r="E21">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F21">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G21" s="1">
-        <v>88.90000000000001</v>
+        <v>97.2</v>
       </c>
       <c r="H21" s="1">
-        <v>11.1</v>
+        <v>2.8</v>
       </c>
       <c r="I21" s="2">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -3309,19 +3309,19 @@
         <v>36</v>
       </c>
       <c r="E22">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G22" s="1">
-        <v>91.7</v>
+        <v>97.2</v>
       </c>
       <c r="H22" s="1">
-        <v>8.300000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="I22" s="2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -3341,19 +3341,19 @@
         <v>114</v>
       </c>
       <c r="E23">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="F23">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="G23" s="1">
-        <v>81.59999999999999</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="H23" s="1">
-        <v>18.4</v>
+        <v>4.4</v>
       </c>
       <c r="I23" s="2">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -3577,19 +3577,19 @@
         <v>795</v>
       </c>
       <c r="E30">
-        <v>725</v>
+        <v>738</v>
       </c>
       <c r="F30">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="G30" s="1">
-        <v>91.2</v>
+        <v>92.8</v>
       </c>
       <c r="H30" s="1">
-        <v>8.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="I30" s="2">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J30">
         <v>0</v>

--- a/academias/Laboratorio Clínico - Estadisticos 20222.xlsx
+++ b/academias/Laboratorio Clínico - Estadisticos 20222.xlsx
@@ -2898,19 +2898,19 @@
         <v>43</v>
       </c>
       <c r="E10">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G10" s="1">
-        <v>93</v>
+        <v>95.3</v>
       </c>
       <c r="H10" s="1">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="I10" s="2">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2930,19 +2930,19 @@
         <v>43</v>
       </c>
       <c r="E11">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G11" s="1">
-        <v>93</v>
+        <v>95.3</v>
       </c>
       <c r="H11" s="1">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="I11" s="2">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -3577,16 +3577,16 @@
         <v>795</v>
       </c>
       <c r="E30">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="F30">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G30" s="1">
-        <v>92.8</v>
+        <v>93</v>
       </c>
       <c r="H30" s="1">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="I30" s="2">
         <v>8.300000000000001</v>
